--- a/Results/Phase 2/Carbon dioxide/carbon dioxide photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide photochemical ozone formation results.xlsx
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="F8" t="n">
         <v>0.000166677678684661</v>
@@ -2608,16 +2608,16 @@
         <v>0.000166677678684661</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="L8" t="n">
         <v>0.000166677678684661</v>
@@ -2626,31 +2626,31 @@
         <v>0.000166677678684661</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="O8" t="n">
         <v>0.000166677678684661</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="Q8" t="n">
         <v>0.000166677678684661</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="S8" t="n">
         <v>0.0001672824409636718</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="U8" t="n">
         <v>0.000166677678684661</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="W8" t="n">
         <v>0.000166677678684661</v>
@@ -2659,13 +2659,13 @@
         <v>0.000166677678684661</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="Z8" t="n">
         <v>0.000166677678684661</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0001666776786846611</v>
+        <v>0.000166677678684661</v>
       </c>
       <c r="AB8" t="n">
         <v>0.000166677678684661</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008989929246224825</v>
+        <v>0.0008989929246224723</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003661717317255166</v>
+        <v>0.0003661717317255165</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001380989605336883</v>
+        <v>0.001380989605336868</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005637211881502272</v>
+        <v>0.0005637211881502268</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005881008877801232</v>
+        <v>0.0005881008877801233</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001142273887585467</v>
+        <v>0.001142273887585463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001442661127863964</v>
+        <v>0.001442661127863961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00142201266811987</v>
+        <v>0.001422012668119856</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001323335233942134</v>
+        <v>0.001323335233942123</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00148265575406051</v>
+        <v>0.001482655754060497</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001085699580836472</v>
+        <v>0.001085699580836455</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00332187600242498</v>
+        <v>0.003321876002424976</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0009334650389533943</v>
+        <v>0.0009334650389533879</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0008012157351830795</v>
+        <v>0.0008012157351830847</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001093065893108759</v>
+        <v>0.00109306589310876</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0006167482990684733</v>
+        <v>0.0006167482990684697</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001168282419534196</v>
+        <v>0.00116828241953419</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001137003128678892</v>
+        <v>0.001137003128678888</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001299247953364304</v>
+        <v>0.001299247953364295</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001397579250768248</v>
+        <v>0.001397579250768238</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000693899079286798</v>
+        <v>0.0006938990792867962</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002049014932175569</v>
+        <v>0.002049014932175564</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001749452102623292</v>
+        <v>0.001749452102623283</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001950206761395754</v>
+        <v>0.001950206761395756</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0008034255974482497</v>
+        <v>0.000803425597448248</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001729109353673827</v>
+        <v>0.001729109353673815</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.002081887906197054</v>
+        <v>0.002081887906197052</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001543494455410891</v>
+        <v>0.0001543494455410647</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002112755407199176</v>
+        <v>0.0002112755407199179</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000176504684050594</v>
+        <v>0.0001765046840505944</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001604817580080092</v>
+        <v>0.0001604817580080094</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002245794018563058</v>
+        <v>0.0002245794018563002</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002105248767267865</v>
+        <v>0.0002105248767267798</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002166154322661337</v>
+        <v>0.000216615432266134</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000167427596642864</v>
+        <v>0.0001674275966428413</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001798187793196291</v>
+        <v>0.0001798187793196229</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00017678140103777</v>
+        <v>0.0001767814010377681</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001429180339065123</v>
+        <v>0.0001429180339064865</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001840968999843187</v>
+        <v>0.0001840968999843029</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001911611537244611</v>
+        <v>0.0001911611537244591</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002125292437792013</v>
+        <v>0.0002125292437791905</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001482492802283477</v>
+        <v>0.0001482492802283353</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002703024720134855</v>
+        <v>0.0002703024720134979</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001532689382774118</v>
+        <v>0.0001532689382774046</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002125178121212515</v>
+        <v>0.0002125178121212704</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002758927482920449</v>
+        <v>0.000275892748292045</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001751453665572967</v>
+        <v>0.001751453665572934</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001556457119401336</v>
+        <v>0.001556457119401323</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001927135795802587</v>
+        <v>0.001927135795802554</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001626047955455472</v>
+        <v>0.001626047955455468</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001636275348704126</v>
+        <v>0.001636275348704102</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001840126719823679</v>
+        <v>0.001840126719823648</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00194961434158012</v>
+        <v>0.001949614341580101</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001942088220469859</v>
+        <v>0.001942088220469832</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001892317321404832</v>
+        <v>0.001892317321404808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001964191913188154</v>
+        <v>0.001964191913188133</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001819506049342729</v>
+        <v>0.001819506049342676</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002637170182221209</v>
+        <v>0.002637170182221171</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001764018346454574</v>
+        <v>0.001764018346454556</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001715815028180025</v>
+        <v>0.001715815028180005</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001822190983666355</v>
+        <v>0.001822190983666312</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001648578813842259</v>
+        <v>0.001648578813842219</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001849606524311386</v>
+        <v>0.001849606524311353</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001838205590094604</v>
+        <v>0.001838205590094559</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001897341923517523</v>
+        <v>0.001897341923517483</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00193318252675688</v>
+        <v>0.001933182526756857</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001589603812363313</v>
+        <v>0.001589603812363314</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00217062318308585</v>
+        <v>0.00217062318308582</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002061436049358387</v>
+        <v>0.002061436049358377</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002134608765100732</v>
+        <v>0.002134608765100701</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001716620497026172</v>
+        <v>0.001716620497026127</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00205402135624293</v>
+        <v>0.002054021356242899</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002184265723908665</v>
+        <v>0.002184265723908618</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00148003986149297</v>
+        <v>0.001480039861492968</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001499999276662701</v>
+        <v>0.001499999276662672</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001484912086636914</v>
+        <v>0.001484912086636918</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001480413197259554</v>
+        <v>0.0014804131972595</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001505637855888109</v>
+        <v>0.001505637855888111</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001486711013478753</v>
+        <v>0.001486711013478763</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001505339168208911</v>
+        <v>0.001505339168208876</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001484806693998205</v>
+        <v>0.001484806693998164</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001489323134579274</v>
+        <v>0.001489323134579247</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001488216045862221</v>
+        <v>0.001488216045862189</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001475873246186603</v>
+        <v>0.001475873246186554</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001490882459325299</v>
+        <v>0.001490882459325302</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00140636174194262</v>
+        <v>0.001406361741942632</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001501245714769116</v>
+        <v>0.001501245714769085</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001477816422868269</v>
+        <v>0.001477816422868232</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001522303378052994</v>
+        <v>0.001522303378052967</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001479646029283371</v>
+        <v>0.001479646029283319</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00150124154806403</v>
+        <v>0.001501241548064003</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001526001695918102</v>
+        <v>0.001526001695918101</v>
       </c>
     </row>
     <row r="6">
@@ -5366,82 +5366,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0003782842239763131</v>
+        <v>0.0003782842239763136</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001832876778046643</v>
+        <v>0.0001832876778046644</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005539663542059306</v>
+        <v>0.0005539663542059313</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002528785138588309</v>
+        <v>0.0002528785138588312</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002631059071074618</v>
+        <v>0.0002631059071074621</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004562566488131363</v>
+        <v>0.0004562566488131212</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005764448999834711</v>
+        <v>0.0005764448999834751</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005689187788732068</v>
+        <v>0.0005689187788732091</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005214111232361728</v>
+        <v>0.0005214111232361712</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0005910224715915002</v>
+        <v>0.0005910224715915115</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004463366077460649</v>
+        <v>0.0004463366077460641</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001264000740624543</v>
+        <v>0.001264000740624541</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0003908489048579248</v>
+        <v>0.0003908489048579357</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003319449571694863</v>
+        <v>0.0003319449571694726</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000438320912655816</v>
+        <v>0.0004383209126558185</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002754093722455999</v>
+        <v>0.0002754093722456</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004764370827147311</v>
+        <v>0.0004764370827147308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.000465036148497952</v>
+        <v>0.0004650361484979538</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005241724819208633</v>
+        <v>0.0005241724819208717</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005493124557463206</v>
+        <v>0.0005493124557463106</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002900358923974169</v>
+        <v>0.0002900358923974185</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0007867531120753091</v>
+        <v>0.0007867531120753043</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0006775659783478471</v>
+        <v>0.0006775659783478343</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0007614393235040775</v>
+        <v>0.0007614393235040768</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.000343451055429518</v>
+        <v>0.0003434510554295193</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.000680851914646276</v>
+        <v>0.0006808519146462791</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0008110962823119889</v>
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001068704198963435</v>
+        <v>0.0001068704198963402</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001268298350660294</v>
+        <v>0.0001268298350660298</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001117426450402704</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001072437556628655</v>
+        <v>0.0001072437556628656</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001217677848775614</v>
+        <v>0.0001217677848775833</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001158048153101399</v>
+        <v>0.0001158048153101163</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="M7" t="n">
         <v>0.0001321697266122329</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000111637252401539</v>
+        <v>0.0001116372524014978</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001054530635687182</v>
+        <v>0.0001054530635687149</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001043459748516798</v>
+        <v>0.0001043459748516718</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001027038045899445</v>
+        <v>0.0001027038045899541</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001070123883147609</v>
+        <v>0.0001070123883147705</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001067938219767195</v>
+        <v>0.0001067938219767196</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001173756437585585</v>
+        <v>0.0001173756437585709</v>
       </c>
       <c r="X7" t="n">
-        <v>9.394635185772313e-05</v>
+        <v>9.394635185772374e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.000149133936456341</v>
+        <v>0.0001491339364563616</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001064765876866936</v>
+        <v>0.0001064765876866641</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001280721064673632</v>
+        <v>0.00012807210646736</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001528322543214576</v>
+        <v>0.0001528322543214577</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0002460480338797969</v>
+        <v>0.0002460480338797972</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0002484607445980711</v>
+        <v>0.0002484607445980713</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009918190221165836</v>
+        <v>0.0009918190221165778</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004205295658459787</v>
+        <v>0.0004205295658459788</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001509822295976328</v>
+        <v>0.001509822295976331</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0006369181904334061</v>
+        <v>0.0006369181904334066</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0006608509126190145</v>
+        <v>0.000660850912619015</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001253273800385582</v>
+        <v>0.001253273800385585</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001576100865624557</v>
+        <v>0.001576100865624556</v>
       </c>
       <c r="I9" t="n">
         <v>0.001553909904201857</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001450002784287687</v>
+        <v>0.001450002784287686</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001619083209975764</v>
+        <v>0.001619083209975766</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001192473223773961</v>
+        <v>0.001192473223773957</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003591294985257947</v>
+        <v>0.003591294985257946</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00102886630645434</v>
+        <v>0.001028866306454338</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0008867375842872914</v>
+        <v>0.000886737584287293</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001200389821597127</v>
+        <v>0.001200389821597126</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0006884898791656458</v>
+        <v>0.0006884898791656468</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001281225247432393</v>
+        <v>0.001281225247432392</v>
       </c>
       <c r="S9" t="n">
         <v>0.001247609300029928</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001421974298206424</v>
+        <v>0.001421974298206421</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001527651237521905</v>
+        <v>0.001527651237521908</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007772349606259659</v>
+        <v>0.0007772349606259688</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002227751112022901</v>
+        <v>0.002227751112022898</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001905810043456257</v>
+        <v>0.001905810043456259</v>
       </c>
       <c r="Y9" t="n">
         <v>0.002121561675464591</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0008891125298708185</v>
+        <v>0.0008891125298708175</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001883947630338579</v>
+        <v>0.001883947630338577</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002260271367227555</v>
+        <v>0.002260271367227554</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0001915484487782776</v>
+        <v>0.0001915484487782777</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002207754557597078</v>
+        <v>0.0002207754557597081</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0002012873553374603</v>
+        <v>0.0002012873553374608</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002670247928070276</v>
+        <v>0.0002670247928070279</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002540621662564833</v>
+        <v>0.0002540621662564836</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0002056035768690233</v>
+        <v>0.0002056035768690236</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0002189204179394768</v>
+        <v>0.0002189204179394767</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0002156561384186723</v>
+        <v>0.0002156561384186727</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0001792630765164323</v>
+        <v>0.0001792630765164325</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0002235181270087375</v>
+        <v>0.0002235181270087379</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0002369410089150104</v>
+        <v>0.0002369410089150106</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002540744518934304</v>
+        <v>0.0002540744518934307</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0001849925828781196</v>
+        <v>0.0001849925828781198</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.000316163513009892</v>
+        <v>0.0003161635130098921</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0001903872243914601</v>
+        <v>0.0001903872243914604</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0002540621662564612</v>
+        <v>0.0002540621662564616</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0003193629713791514</v>
+        <v>0.0003193629713791518</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00134866638322165</v>
+        <v>0.001348666383221597</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001358261242657479</v>
+        <v>0.00135826124265745</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001287520938300905</v>
+        <v>0.001287520938300891</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001359447151339581</v>
+        <v>0.001359447151339523</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001724826651061661</v>
+        <v>0.001724826651061652</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00144402335332283</v>
+        <v>0.001444023353322798</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001979438434882903</v>
+        <v>0.001979438434882878</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001550383865862273</v>
+        <v>0.001550383865862229</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001562147407513189</v>
+        <v>0.001562147407513196</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001853338324332827</v>
+        <v>0.001853338324332819</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00201201603757162</v>
+        <v>0.002012016037571576</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002001108615634991</v>
+        <v>0.002001108615634963</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001939254855340848</v>
+        <v>0.001939254855340816</v>
       </c>
       <c r="K12" t="n">
-        <v>0.002033142953018577</v>
+        <v>0.002033142953018562</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001823453294547014</v>
+        <v>0.001823453294546997</v>
       </c>
       <c r="M12" t="n">
-        <v>0.003002535201133646</v>
+        <v>0.003002535201133601</v>
       </c>
       <c r="N12" t="n">
-        <v>0.001743036333561704</v>
+        <v>0.001743036333561679</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001673176451762999</v>
+        <v>0.001673176451762969</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001827344503725171</v>
+        <v>0.001827344503725132</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001575732662530954</v>
+        <v>0.001575732662530939</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001867077171463943</v>
+        <v>0.001867077171463912</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001850554078339047</v>
+        <v>0.001850554078339032</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001936258909682888</v>
+        <v>0.001936258909682857</v>
       </c>
       <c r="U12" t="n">
-        <v>0.001988201813107793</v>
+        <v>0.001988201813107758</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001547426914142277</v>
+        <v>0.001547426914142282</v>
       </c>
       <c r="W12" t="n">
-        <v>0.002332318707527261</v>
+        <v>0.002332318707527231</v>
       </c>
       <c r="X12" t="n">
-        <v>0.00217407648418705</v>
+        <v>0.002174076484187031</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.002280123898672813</v>
+        <v>0.002280123898672787</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.00167434379792086</v>
+        <v>0.001674343797920843</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.002163330552098524</v>
+        <v>0.002163330552098506</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.002348303240069462</v>
+        <v>0.002348303240069434</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.00133147331045616</v>
+        <v>0.001331473310456109</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0013458391277373</v>
+        <v>0.00134583912773727</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001336260230726023</v>
+        <v>0.00133626023072602</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001368571853185964</v>
+        <v>0.00136857185318594</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00135141962443139</v>
+        <v>0.00135141962443136</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001362200392549334</v>
+        <v>0.001362200392549282</v>
       </c>
       <c r="N13" t="n">
-        <v>0.001338381763386106</v>
+        <v>0.001338381763386069</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001344927329468243</v>
+        <v>0.001344927329468236</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001343322853061191</v>
+        <v>0.001343322853061149</v>
       </c>
       <c r="Q13" t="n">
         <v>0.00132543473752747</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001347187220412346</v>
+        <v>0.001347187220412348</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001281858695223636</v>
+        <v>0.001281858695223624</v>
       </c>
       <c r="W13" t="n">
-        <v>0.00136220643125236</v>
+        <v>0.001362206431252331</v>
       </c>
       <c r="X13" t="n">
-        <v>0.00132825093562658</v>
+        <v>0.001328250935626536</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.00139272478394317</v>
+        <v>0.001392724783943171</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001330902539135829</v>
+        <v>0.001330902539135808</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.001362200392549323</v>
+        <v>0.00136220039254927</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0013942973991056</v>
+        <v>0.001394297399105591</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001694951981912831</v>
+        <v>0.0001694951981912833</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001698617392223062</v>
+        <v>0.0001698617392223064</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0001694951981912831</v>
+        <v>0.0001694951981912833</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001694951981912831</v>
+        <v>0.0001694951981912833</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001775104675227241</v>
+        <v>0.0001775104675227243</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001694951981912831</v>
+        <v>0.0001694951981912833</v>
       </c>
       <c r="V14" t="n">
         <v>0.0001700580947839404</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0001694951981912831</v>
+        <v>0.0001694951981912833</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0001694951981912831</v>
+        <v>0.0001694951981912833</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0001786963762048201</v>
+        <v>0.0001786963762048204</v>
       </c>
     </row>
     <row r="15">
@@ -6158,82 +6158,82 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0005440758759269073</v>
+        <v>0.0005440758759269075</v>
       </c>
       <c r="C15" t="n">
-        <v>0.000263272578188074</v>
+        <v>0.0002632725781880743</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0007986876597481536</v>
+        <v>0.0007986876597481529</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000369633090727515</v>
+        <v>0.0003696330907275157</v>
       </c>
       <c r="F15" t="n">
-        <v>0.000381396632378462</v>
+        <v>0.0003813966323784619</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006633863711845411</v>
+        <v>0.0006633863711845379</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0008312652624368664</v>
+        <v>0.0008312652624368677</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0008203578405002406</v>
+        <v>0.0008203578405002408</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0007604502113415493</v>
+        <v>0.0007604502113415466</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0008523921778838214</v>
+        <v>0.0008523921778838209</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0006427025194122643</v>
+        <v>0.0006427025194122609</v>
       </c>
       <c r="M15" t="n">
-        <v>0.001821784425998892</v>
+        <v>0.001821784425998891</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0005622855584269513</v>
+        <v>0.0005622855584269506</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0004832244986147039</v>
+        <v>0.0004832244986147057</v>
       </c>
       <c r="P15" t="n">
-        <v>0.000637392550576871</v>
+        <v>0.0006373925505768716</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0003949818873962114</v>
+        <v>0.0003949818873962112</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0006863263963291841</v>
+        <v>0.0006863263963291829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0006698033032042936</v>
+        <v>0.0006698033032042929</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0007555081345481332</v>
+        <v>0.0007555081345481325</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0007982498599595063</v>
+        <v>0.000798249859959504</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0004299640706253142</v>
+        <v>0.0004299640706253139</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001142366754378965</v>
+        <v>0.001142366754378966</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0009841245310387623</v>
+        <v>0.0009841245310387632</v>
       </c>
       <c r="Y15" t="n">
         <v>0.001099373123538063</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0004935930227861026</v>
+        <v>0.0004935930227861027</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0009825797769637754</v>
+        <v>0.0009825797769637741</v>
       </c>
       <c r="AB15" t="n">
         <v>0.001167552464934708</v>
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0001507225353214058</v>
+        <v>0.000150722535321406</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0001650883526025393</v>
+        <v>0.0001650883526025395</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001555094555912833</v>
+        <v>0.0001555094555912835</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001786199000376768</v>
+        <v>0.000178619900037677</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001726149804320593</v>
+        <v>0.0001726149804320596</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0001814496174145838</v>
+        <v>0.0001814496174145841</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0001576309882513575</v>
+        <v>0.0001576309882513578</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0001549753763199573</v>
+        <v>0.0001549753763199574</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0001533708999129062</v>
+        <v>0.0001533708999129065</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0001446839623927271</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0001572352672640686</v>
+        <v>0.0001572352672640688</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0001643958517066743</v>
+        <v>0.0001643958517066745</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0001722544781040751</v>
+        <v>0.0001722544781040752</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0001382989824782763</v>
+        <v>0.0001382989824782765</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0002119740088084274</v>
+        <v>0.0002119740088084276</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0001501517640010988</v>
+        <v>0.000150151764001099</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0001814496174145731</v>
+        <v>0.0001814496174145732</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0002135466239708549</v>
+        <v>0.0002135466239708551</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007864501702086282</v>
+        <v>0.0007864501702086272</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003445447340891497</v>
+        <v>0.0003445447340891496</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009483018204527985</v>
+        <v>0.0009483018204527886</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004054191859237954</v>
+        <v>0.0004054191859237963</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0006681630973155918</v>
+        <v>0.0006681630973155893</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001035275824415717</v>
+        <v>0.001035275824415703</v>
       </c>
       <c r="H2" t="n">
         <v>0.001336963263071835</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001280920025986815</v>
+        <v>0.001280920025986811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001251219394807741</v>
+        <v>0.001251219394807734</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001722320768972448</v>
+        <v>0.001722320768972447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009661348573545975</v>
+        <v>0.0009661348573545897</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002775304284634116</v>
+        <v>0.002775304284634112</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0006796254961011342</v>
+        <v>0.0006796254961011306</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0007769149478630511</v>
+        <v>0.0007769149478630464</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0009854298254895763</v>
+        <v>0.0009854298254895742</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0006093393681548875</v>
+        <v>0.0006093393681548829</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00122681803505801</v>
+        <v>0.001226818035058004</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00106386910093479</v>
+        <v>0.001063869100934788</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001353463424699109</v>
+        <v>0.001353463424699105</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001456185302535848</v>
+        <v>0.00145618530253584</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0009433020610790601</v>
+        <v>0.0009433020610790551</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001786699438626089</v>
+        <v>0.001786699438626088</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0019444031393201</v>
+        <v>0.001944403139320094</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.002809166893967335</v>
+        <v>0.002809166893967326</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0006868450937755541</v>
+        <v>0.0006868450937755511</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001757691926986576</v>
+        <v>0.001757691926986572</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001898265353631276</v>
+        <v>0.001898265353631273</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001518264390638499</v>
+        <v>0.000151826439063841</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002082257586169049</v>
+        <v>0.0002082257586169047</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000173779732072023</v>
+        <v>0.0001737797320720226</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001585614817009984</v>
+        <v>0.0001585614817009981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002209874546180113</v>
+        <v>0.0002209874546180144</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002074625147932227</v>
+        <v>0.0002074625147932234</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002121465165130451</v>
+        <v>0.0002121465165130448</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001647055331030375</v>
+        <v>0.0001647055331030296</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001769081147757479</v>
+        <v>0.0001769081147757446</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001739169671572053</v>
+        <v>0.0001739169671572051</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0001405690201599495</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001811211748663642</v>
+        <v>0.0001811211748663646</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001889740791241917</v>
+        <v>0.0001889740791241874</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002091207069507597</v>
+        <v>0.0002091207069507577</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001458191218129301</v>
+        <v>0.0001458191218129254</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002660146870013856</v>
+        <v>0.0002660146870013864</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001507623777489669</v>
+        <v>0.0001507623777489699</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002091094492904193</v>
+        <v>0.0002091094492904169</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002714090472093695</v>
+        <v>0.0002714090472093692</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001701660224626929</v>
+        <v>0.001701660224626964</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00154002928647716</v>
+        <v>0.001540029286477188</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001760653250582899</v>
+        <v>0.001760653250582895</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001559710524786696</v>
+        <v>0.001559710524786724</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001657154852509968</v>
+        <v>0.001657154852509986</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001792354253727062</v>
+        <v>0.001792354253727064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001902315782524457</v>
+        <v>0.001902315782524472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00188188868069988</v>
+        <v>0.001881888680699895</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001860889515011196</v>
+        <v>0.001860889515011218</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002042774068328931</v>
+        <v>0.002042774068328946</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00176715318312751</v>
+        <v>0.001767153183127514</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002428504286913906</v>
+        <v>0.002428504286913922</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001662723885313403</v>
+        <v>0.001662723885313407</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001698184748050204</v>
+        <v>0.001698184748050198</v>
       </c>
       <c r="P4" t="n">
         <v>0.001774185972439757</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001637105417018379</v>
+        <v>0.001637105417018384</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001862169140303984</v>
+        <v>0.001862169140304001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001802776167259064</v>
+        <v>0.001802776167259065</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001908329897682918</v>
+        <v>0.001908329897682923</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001945770815933218</v>
+        <v>0.001945770815933221</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001695112082870597</v>
+        <v>0.001695112082870594</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002066239337445177</v>
+        <v>0.002066239337445201</v>
       </c>
       <c r="X4" t="n">
         <v>0.002123720484497796</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002438916718498027</v>
+        <v>0.00243891671849803</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001665355343888933</v>
+        <v>0.001665355343888929</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002055666440075973</v>
+        <v>0.002055666440076007</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002108468880637352</v>
+        <v>0.00210846888063734</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001470347326752752</v>
+        <v>0.001470347326752754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001490342620655755</v>
+        <v>0.001490342620655774</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001475280663905524</v>
+        <v>0.001475280663905548</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00147141104766274</v>
+        <v>0.001471411047662768</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001495555704792594</v>
+        <v>0.001495555704792618</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001480452388657989</v>
+        <v>0.001480452388657996</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001494263378551876</v>
+        <v>0.001494263378551902</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001475041605296078</v>
+        <v>0.001475041605296093</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001479489303025832</v>
+        <v>0.001479489303025843</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001478399064842702</v>
+        <v>0.001478399064842707</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001466244129753565</v>
+        <v>0.001466244129753599</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001481024913956611</v>
+        <v>0.00148102491395664</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001420168391214416</v>
+        <v>0.001420168391214417</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001491230414614268</v>
+        <v>0.001491230414614299</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001468157730156272</v>
+        <v>0.001468157730156279</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001511967602259876</v>
+        <v>0.001511967602259904</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001469959488898315</v>
+        <v>0.001469959488898307</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001491226311329269</v>
+        <v>0.001491226311329284</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001515498860457814</v>
+        <v>0.001515498860457808</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0003365065507048615</v>
+        <v>0.0003365065507048582</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001748756125550917</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0003954995766608298</v>
+        <v>0.000395499576660822</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001945568508646302</v>
+        <v>0.0001945568508646305</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002920011785879002</v>
+        <v>0.0002920011785878993</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000416539239150619</v>
+        <v>0.0004165392391506102</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005371621086023877</v>
+        <v>0.0005371621086023856</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005167350067778128</v>
+        <v>0.0005167350067778062</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004946236656742162</v>
+        <v>0.0004946236656742173</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0006776203944068626</v>
+        <v>0.0006776203944068633</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004019995092054415</v>
+        <v>0.0004019995092054341</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001063350612991835</v>
+        <v>0.001063350612991834</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002975702113913362</v>
+        <v>0.0002975702113913297</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003223697334737578</v>
+        <v>0.0003223697334737514</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0003983709578633141</v>
+        <v>0.0003983709578633049</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000271951743096312</v>
+        <v>0.0002719517430963047</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004970154663819158</v>
+        <v>0.0004970154663819099</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004376224933369937</v>
+        <v>0.0004376224933369875</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005431762237608494</v>
+        <v>0.0005431762237608435</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005699558013567763</v>
+        <v>0.0005699558013567695</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0003808357342323283</v>
+        <v>0.0003808357342323245</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0006904243228687346</v>
+        <v>0.0006904243228687428</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0007479054699213526</v>
+        <v>0.0007479054699213443</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001073763044575957</v>
+        <v>0.001073763044575947</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0003002016699668655</v>
+        <v>0.0003002016699668594</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006905127661539054</v>
+        <v>0.0006905127661539059</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0007433152067152837</v>
+        <v>0.0007433152067152824</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001051936528306829</v>
+        <v>0.0001051936528306835</v>
       </c>
       <c r="C7" t="n">
         <v>0.0001251889467336862</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001101269899834557</v>
+        <v>0.0001101269899834555</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001062573737406734</v>
+        <v>0.0001062573737406733</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001197406902161521</v>
+        <v>0.0001197406902161508</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001141865393210101</v>
+        <v>0.000114186539321011</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000129109704629808</v>
+        <v>0.0001291097046298078</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001098879313740089</v>
+        <v>0.0001098879313739991</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001036742884493886</v>
+        <v>0.0001036742884493821</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001025840502662583</v>
+        <v>0.000102584050266254</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.000101090455831498</v>
+        <v>0.0001010904558314939</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001052098993801682</v>
+        <v>0.0001052098993801645</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001058920425761523</v>
+        <v>0.0001058920425761528</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001154154000378256</v>
+        <v>0.0001154154000378282</v>
       </c>
       <c r="X7" t="n">
-        <v>9.234271557982802e-05</v>
+        <v>9.234271557981879e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001468139283378092</v>
+        <v>0.0001468139283378071</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001048058149762467</v>
+        <v>0.0001048058149762363</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001260726374072005</v>
+        <v>0.000126072637407203</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001503451865357443</v>
+        <v>0.000150345186535744</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451427</v>
       </c>
       <c r="M8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="P8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0002382227790606471</v>
+        <v>0.0002382227790606472</v>
       </c>
       <c r="T8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="W8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="X8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.000240564220345143</v>
+        <v>0.0002405642203451425</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008716017131951855</v>
+        <v>0.0008716017131951875</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0003976343247771864</v>
+        <v>0.000397634324777186</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00104554416562415</v>
+        <v>0.001045544165624147</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004672954604726296</v>
+        <v>0.0004672954604726303</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000746830746577829</v>
+        <v>0.0007468307465778245</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001139015387721997</v>
+        <v>0.001139015387721988</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001463239780044795</v>
+        <v>0.001463239780044796</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001403009945588861</v>
+        <v>0.00140300994558886</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001372860553888608</v>
+        <v>0.001372860553888605</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001877384643795889</v>
+        <v>0.001877384643795888</v>
       </c>
       <c r="L9" t="n">
         <v>0.001064709383700547</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003005765231111829</v>
+        <v>0.003005765231111826</v>
       </c>
       <c r="N9" t="n">
         <v>0.0007567969165425095</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0008613541812315472</v>
+        <v>0.0008613541812315459</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001085445743644205</v>
+        <v>0.001085445743644208</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0006812602046939576</v>
+        <v>0.0006812602046939582</v>
       </c>
       <c r="R9" t="n">
         <v>0.001344866374181035</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00116974466748655</v>
+        <v>0.001169744667486548</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001480972553078574</v>
+        <v>0.001480972553078575</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001591368062312342</v>
+        <v>0.001591368062312338</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001044949953508957</v>
+        <v>0.001044949953508955</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001946572592554979</v>
+        <v>0.001946572592554977</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002116057231200653</v>
+        <v>0.002116057231200652</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003045421423830731</v>
+        <v>0.003045421423830723</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.000764555839748696</v>
+        <v>0.0007645558397486966</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001915398133067993</v>
+        <v>0.001915398133067994</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002063826139733381</v>
+        <v>0.002063826139733376</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0001895696919064951</v>
+        <v>0.0001895696919064949</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000218351846851771</v>
+        <v>0.0002183518468517708</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0001991603666463342</v>
+        <v>0.0001991603666463341</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002638972421033564</v>
+        <v>0.0002638972421033561</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002511319142644143</v>
+        <v>0.0002511319142644142</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0002034108927769211</v>
+        <v>0.0002034108927769208</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0002165250437844265</v>
+        <v>0.0002165250437844261</v>
       </c>
       <c r="P10" t="n">
-        <v>0.000213310448495707</v>
+        <v>0.0002133104484957065</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0001774713101525211</v>
+        <v>0.0001774713101525209</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0002210528320602141</v>
+        <v>0.0002210528320602137</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0002342714159773533</v>
+        <v>0.0002342714159773529</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002511440129056104</v>
+        <v>0.0002511440129056101</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0001831136100959766</v>
+        <v>0.0001831136100959762</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0003122881433702718</v>
+        <v>0.0003122881433702714</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0001884261420300104</v>
+        <v>0.0001884261420300103</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0002511319142643836</v>
+        <v>0.0002511319142643832</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0003154388031714894</v>
+        <v>0.0003154388031714891</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001340546703461823</v>
+        <v>0.001340546703461832</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401097</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001347243902458319</v>
+        <v>0.00134724390245834</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001296034740585439</v>
+        <v>0.001296034740585447</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001348394780401073</v>
+        <v>0.001348394780401096</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001658565757729955</v>
+        <v>0.00165856575772996</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001425598731597066</v>
+        <v>0.001425598731597085</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001744062897091992</v>
+        <v>0.001744062897092021</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001459838951529021</v>
+        <v>0.001459838951529047</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001597237654255166</v>
+        <v>0.001597237654255194</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001790006380068377</v>
+        <v>0.001790006380068398</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001949370915108011</v>
+        <v>0.001949370915108036</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001919766419607782</v>
+        <v>0.001919766419607784</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001897099149838478</v>
+        <v>0.001897099149838488</v>
       </c>
       <c r="K12" t="n">
-        <v>0.002152933648861354</v>
+        <v>0.002152933648861384</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001753483089218183</v>
+        <v>0.001753483089218205</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00270756140637543</v>
+        <v>0.002707561406375453</v>
       </c>
       <c r="N12" t="n">
-        <v>0.001602136280268989</v>
+        <v>0.001602136280269017</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001653528835137579</v>
+        <v>0.001653528835137598</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001763675537532024</v>
+        <v>0.001763675537532045</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001565008065220375</v>
+        <v>0.001565008065220397</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001891187375457005</v>
+        <v>0.001891187375456997</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001805110602630709</v>
+        <v>0.001805110602630733</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001958087024063432</v>
+        <v>0.001958087024063454</v>
       </c>
       <c r="U12" t="n">
-        <v>0.002012349224613684</v>
+        <v>0.00201234922461371</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001691410786908781</v>
+        <v>0.001691410786908766</v>
       </c>
       <c r="W12" t="n">
-        <v>0.00218694128537922</v>
+        <v>0.002186941285379212</v>
       </c>
       <c r="X12" t="n">
-        <v>0.002270247295888254</v>
+        <v>0.002270247295888277</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.00272705343369889</v>
+        <v>0.002727053433698904</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.001605949988362643</v>
+        <v>0.001605949988362674</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.00217161824566076</v>
+        <v>0.002171618245660791</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.002244574386004264</v>
+        <v>0.002244574386004286</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.001323329672695976</v>
+        <v>0.001323329672695983</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001337476833887123</v>
+        <v>0.001337476833887138</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001328043733256567</v>
+        <v>0.001328043733256576</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001359863554039379</v>
+        <v>0.001359863554039399</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001345740993798267</v>
+        <v>0.001345740993798275</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001353589070737528</v>
+        <v>0.001353589070737538</v>
       </c>
       <c r="N13" t="n">
-        <v>0.001330132974956186</v>
+        <v>0.001330132974956182</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001336578913717235</v>
+        <v>0.001336578913717237</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001334998858373905</v>
+        <v>0.001334998858373926</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001317383010357768</v>
+        <v>0.001317383010357787</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001338804436813013</v>
+        <v>0.001338804436813026</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001292941667189634</v>
+        <v>0.001292941667189632</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001353595017527391</v>
+        <v>0.001353595017527402</v>
       </c>
       <c r="X13" t="n">
-        <v>0.001320156344284315</v>
+        <v>0.001320156344284323</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.001383648912769801</v>
+        <v>0.001383648912769817</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001322767588847025</v>
+        <v>0.001322767588847033</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.001353589070737514</v>
+        <v>0.001353589070737523</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001385197542194907</v>
+        <v>0.001385197542194941</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000165369149555199</v>
+        <v>0.0001653691495551988</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001657321680444306</v>
+        <v>0.0001657321680444303</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="O14" t="n">
-        <v>0.000165369149555199</v>
+        <v>0.0001653691495551988</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000165369149555199</v>
+        <v>0.0001653691495551988</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001733856662982715</v>
+        <v>0.0001733856662982713</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="U14" t="n">
-        <v>0.000165369149555199</v>
+        <v>0.0001653691495551988</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0001659245222945866</v>
+        <v>0.0001659245222945865</v>
       </c>
       <c r="W14" t="n">
-        <v>0.000165369149555199</v>
+        <v>0.0001653691495551988</v>
       </c>
       <c r="X14" t="n">
-        <v>0.000165369149555199</v>
+        <v>0.0001653691495551988</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0001745365442410228</v>
+        <v>0.0001745365442410226</v>
       </c>
     </row>
     <row r="15">
@@ -7634,82 +7634,82 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0004847075215699016</v>
+        <v>0.0004847075215699027</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0002517404954370151</v>
+        <v>0.000251740495437015</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0005702046609319445</v>
+        <v>0.0005702046609319431</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0002859807153689703</v>
+        <v>0.0002859807153689705</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0004233794180951201</v>
+        <v>0.0004233794180951188</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006069807492225017</v>
+        <v>0.0006069807492224976</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00077551267894796</v>
+        <v>0.0007755126789479604</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0007459081834477328</v>
+        <v>0.0007459081834477336</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0007222846144210853</v>
+        <v>0.0007222846144210847</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0009790754127013018</v>
+        <v>0.0009790754127013026</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0005796248530581352</v>
+        <v>0.0005796248530581348</v>
       </c>
       <c r="M15" t="n">
-        <v>0.001533703170215378</v>
+        <v>0.001533703170215376</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0004282780441089392</v>
+        <v>0.0004282780441089391</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0004705032042917049</v>
+        <v>0.0004705032042917041</v>
       </c>
       <c r="P15" t="n">
-        <v>0.000580649906686148</v>
+        <v>0.0005806499066861461</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0003911498290603251</v>
+        <v>0.0003911498290603248</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0007173291392969553</v>
+        <v>0.0007173291392969564</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0006312523664706583</v>
+        <v>0.000631252366470658</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0007842287879033841</v>
+        <v>0.0007842287879033846</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0008293235937678104</v>
+        <v>0.0008293235937678093</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0005613005686179033</v>
+        <v>0.0005613005686179026</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001003915654533347</v>
+        <v>0.001003915654533344</v>
       </c>
       <c r="X15" t="n">
-        <v>0.001087221665042381</v>
+        <v>0.00108722166504238</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.001553195197538841</v>
+        <v>0.001553195197538836</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0004320917522025952</v>
+        <v>0.0004320917522025954</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0009977600095007113</v>
+        <v>0.0009977600095007115</v>
       </c>
       <c r="AB15" t="n">
         <v>0.001070716149844211</v>
@@ -7725,82 +7725,82 @@
         <v>0.0001494714365359258</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000163618597727074</v>
+        <v>0.0001636185977270737</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001541854970965181</v>
+        <v>0.000154185497096518</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001768379231935048</v>
+        <v>0.0001768379231935047</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001709264583808724</v>
+        <v>0.0001709264583808721</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0001797308345774799</v>
+        <v>0.0001797308345774797</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0001562747387961381</v>
+        <v>0.000156274738796138</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0001535532828713618</v>
+        <v>0.0001535532828713617</v>
       </c>
       <c r="P16" t="n">
         <v>0.0001519732275280323</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0001435247741977189</v>
+        <v>0.0001435247741977187</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0001557788059671395</v>
+        <v>0.0001557788059671393</v>
       </c>
       <c r="V16" t="n">
-        <v>0.000162831448898771</v>
+        <v>0.0001628314488987708</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0001705693866815164</v>
+        <v>0.0001705693866815161</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0001371307134384419</v>
+        <v>0.0001371307134384418</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.000209790676609751</v>
+        <v>0.0002097906766097506</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.000148909352686975</v>
+        <v>0.0001489093526869747</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0001797308345774647</v>
+        <v>0.0001797308345774646</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0002113393060348597</v>
+        <v>0.0002113393060348593</v>
       </c>
     </row>
   </sheetData>
@@ -9499,7 +9499,7 @@
         <v>0.0003067490176065081</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001993729394292462</v>
+        <v>0.0001993729394292461</v>
       </c>
       <c r="V2" t="n">
         <v>0.0003842390153815364</v>
@@ -9599,7 +9599,7 @@
         <v>0.0001262126279046011</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002332295283192182</v>
+        <v>0.0002332295283192181</v>
       </c>
       <c r="Z3" t="n">
         <v>0.0001306139078640298</v>
@@ -9812,7 +9812,7 @@
         <v>0.0001581172093917185</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002360080089060175</v>
+        <v>0.0002360080089060176</v>
       </c>
       <c r="I6" t="n">
         <v>0.0002204402786009776</v>
@@ -9866,7 +9866,7 @@
         <v>0.0002355839551018491</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002201181118595455</v>
+        <v>0.0002201181118595454</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0003489791679308647</v>
@@ -9948,7 +9948,7 @@
         <v>9.914235419234403e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>7.85993467226136e-05</v>
+        <v>7.859934672261363e-05</v>
       </c>
       <c r="Y7" t="n">
         <v>0.0001281290671162472</v>
@@ -10209,7 +10209,7 @@
         <v>0.0002079230816843448</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002229461128764228</v>
+        <v>0.0002229461128764229</v>
       </c>
       <c r="X10" t="n">
         <v>0.0001623745276483912</v>
@@ -10218,7 +10218,7 @@
         <v>0.0002773859104880616</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0001671045963799396</v>
+        <v>0.0001671045963799397</v>
       </c>
       <c r="AA10" t="n">
         <v>0.000222935340733112</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001302789787167087</v>
+        <v>0.001302789787167086</v>
       </c>
       <c r="C12" t="n">
         <v>0.001323266204504346</v>
@@ -10631,7 +10631,7 @@
         <v>0.0002334588106290604</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0001824330523108387</v>
+        <v>0.0001824330523108386</v>
       </c>
       <c r="R15" t="n">
         <v>0.0003117559939346131</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide photochemical ozone formation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001421958280719848</v>
+        <v>0.001421958280719843</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004025864841273235</v>
+        <v>0.0004025864841273234</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001376982194244252</v>
+        <v>0.001376982194244246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005684549422587773</v>
+        <v>0.0005684549422587749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00101631853241002</v>
+        <v>0.001016318532410019</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001287151908746347</v>
+        <v>0.001287151908746341</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002145582960861801</v>
+        <v>0.002145582960861794</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001534336296879549</v>
+        <v>0.001534336296879558</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001455002836494213</v>
+        <v>0.001455002836494212</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002585085277580541</v>
+        <v>0.002585085277580534</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001505203804103221</v>
+        <v>0.001505203804103219</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004169059326684182</v>
+        <v>0.004169059326684181</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0018795838758907</v>
+        <v>0.001879583875890691</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001365327262376291</v>
+        <v>0.001365327262376286</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001071079104014463</v>
+        <v>0.001071079104014455</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0009841638758394358</v>
+        <v>0.0009841638758394339</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001487516086975645</v>
+        <v>0.001487516086975639</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001312361331605634</v>
+        <v>0.00131236133160563</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00202213675032514</v>
+        <v>0.002022136750325135</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002168564426457975</v>
+        <v>0.002168564426457968</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008501492282115159</v>
+        <v>0.0008501492282115149</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001944372826122499</v>
+        <v>0.001944372826122495</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001089597280435359</v>
+        <v>0.001089597280435349</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001401170360496939</v>
+        <v>0.00140117036049693</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001001417972435874</v>
+        <v>0.001001417972435875</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001978808334386215</v>
+        <v>0.001978808334386207</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.002347792532035448</v>
+        <v>0.002347792532035447</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000169099842860002</v>
+        <v>0.000169099842860012</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002301195253947166</v>
+        <v>0.0002301195253947164</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001923138653483411</v>
+        <v>0.0001923138653483409</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001764667499075769</v>
+        <v>0.0001764667499075768</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002450028198033209</v>
+        <v>0.0002450028198033136</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002296820666900107</v>
+        <v>0.0002296820666900044</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002374716609664889</v>
+        <v>0.0002374716609664887</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001832344181002244</v>
+        <v>0.0001832344181002246</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001966265331260996</v>
+        <v>0.0001966265331260745</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001933438021395774</v>
+        <v>0.0001933438021395637</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000156745027060677</v>
+        <v>0.0001567450270606717</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002012676788800668</v>
+        <v>0.0002012676788800835</v>
       </c>
       <c r="V3" t="n">
         <v>0.0002084763537879346</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002319792766002044</v>
+        <v>0.0002319792766001943</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001625069196800611</v>
+        <v>0.0001625069196800665</v>
       </c>
       <c r="Y3" t="n">
         <v>0.0002944491468807398</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.000167932054607287</v>
+        <v>0.0001679320546072823</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002319669215111128</v>
+        <v>0.0002319669215111001</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0003002196722093215</v>
+        <v>0.0003002196722093214</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001966224648768993</v>
+        <v>0.001966224648768982</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001593501557053806</v>
+        <v>0.001593501557053798</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00194983139338451</v>
+        <v>0.001949831393384497</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00165120639114618</v>
+        <v>0.001651206391146172</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001816831305599315</v>
+        <v>0.001816831305599308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001917089309160991</v>
+        <v>0.00191708930916098</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002229977347450734</v>
+        <v>0.002229977347450724</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002007185116049913</v>
+        <v>0.002007185116049898</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001967962909759873</v>
+        <v>0.001967962909759871</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00239017078099795</v>
+        <v>0.002390170780997938</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001996566664523942</v>
+        <v>0.001996566664523931</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00297100904849767</v>
+        <v>0.002971009048497663</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002133023804497723</v>
+        <v>0.002133023804497733</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001945583307577757</v>
+        <v>0.001945583307577747</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001838333309091192</v>
+        <v>0.00183833330909118</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001806653729031536</v>
+        <v>0.001806653729031524</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001990119699330602</v>
+        <v>0.001990119699330592</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001926277847769213</v>
+        <v>0.001926277847769202</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002184982653288711</v>
+        <v>0.002184982653288699</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002238353821798546</v>
+        <v>0.002238353821798536</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001694736662174677</v>
+        <v>0.001694736662174678</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002156638616066949</v>
+        <v>0.002156638616066938</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001845082966945204</v>
+        <v>0.001845082966945185</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001958647695951827</v>
+        <v>0.001958647695951798</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001812942644633104</v>
+        <v>0.001812942644633092</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002169189954466918</v>
+        <v>0.002169189954466906</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002305321780648725</v>
+        <v>0.002305321780648718</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001509572459975624</v>
+        <v>0.001509572459975611</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001530639375805048</v>
+        <v>0.001530639375805041</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001514107385483849</v>
+        <v>0.00151410738548384</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001510715192914719</v>
+        <v>0.001510715192914712</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001537238203773707</v>
+        <v>0.001537238203773692</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001521347877609162</v>
+        <v>0.001521347877609165</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001537991511376821</v>
+        <v>0.001537991511376812</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001514724346674122</v>
+        <v>0.001514724346674102</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001519605615342899</v>
+        <v>0.00151960561534288</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001518409098446085</v>
+        <v>0.001518409098446066</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00150506927469434</v>
+        <v>0.001505069274694345</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001521297258471134</v>
+        <v>0.001521297258471123</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001460854434350596</v>
+        <v>0.001460854434350595</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001532491275206338</v>
+        <v>0.00153249127520633</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001507169416894547</v>
+        <v>0.001507169416894525</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001555260809365341</v>
+        <v>0.001555260809365326</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001509146814870371</v>
+        <v>0.001509146814870364</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001532486771921443</v>
+        <v>0.001532486771921444</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001559005517056542</v>
+        <v>0.001559005517056535</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0005739381631284988</v>
+        <v>0.0005739381631284953</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000201215071413312</v>
+        <v>0.0002012150714133121</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005575449077440171</v>
+        <v>0.0005575449077440118</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002589199055056864</v>
+        <v>0.0002589199055056861</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0004245448199588222</v>
+        <v>0.000424544819958822</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0005137374130556612</v>
+        <v>0.0005137374130556568</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008376908618102405</v>
+        <v>0.0008376908618102345</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006148986304094198</v>
+        <v>0.0006148986304094128</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005739184223119603</v>
+        <v>0.0005739184223119559</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009978842953574532</v>
+        <v>0.0009978842953574497</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006042801788834489</v>
+        <v>0.0006042801788834481</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001578722562857177</v>
+        <v>0.001578722562857178</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007407373188572288</v>
+        <v>0.0007407373188572453</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0005422314114724262</v>
+        <v>0.0005422314114724236</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0004349814129858625</v>
+        <v>0.0004349814129858578</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0004143672433910414</v>
+        <v>0.0004143672433910386</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0005978332136901095</v>
+        <v>0.0005978332136901043</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0005339913621287209</v>
+        <v>0.0005339913621287167</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0007926961676482165</v>
+        <v>0.0007926961676482124</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000835001925693214</v>
+        <v>0.0008350019256932114</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0003511649478218017</v>
+        <v>0.0003511649478218011</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0007532867199616176</v>
+        <v>0.0007532867199616154</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0004417310708398747</v>
+        <v>0.0004417310708398651</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0005663612103113332</v>
+        <v>0.0005663612103113119</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0004206561589926113</v>
+        <v>0.0004206561589926076</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0007769034688264249</v>
+        <v>0.0007769034688264218</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0009130352950082318</v>
+        <v>0.0009130352950082319</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001172859743351302</v>
+        <v>0.0001172859743351261</v>
       </c>
       <c r="C7" t="n">
         <v>0.0001383528901645549</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001218208998433561</v>
+        <v>0.000121820899843356</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001184287072742251</v>
+        <v>0.0001184287072742249</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001338863076683771</v>
+        <v>0.0001338863076683707</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001273033901612493</v>
+        <v>0.0001273033901612538</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000145705025736326</v>
+        <v>0.0001457050257363258</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000122437861033629</v>
+        <v>0.0001224378610336158</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001162537192375683</v>
+        <v>0.0001162537192375566</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001150572023407544</v>
+        <v>0.0001150572023407426</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001127827890538479</v>
+        <v>0.000112782789053858</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001179453623658044</v>
+        <v>0.0001179453623658017</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001172827199977187</v>
+        <v>0.0001172827199977186</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001291393791010064</v>
+        <v>0.0001291393791010055</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001038175207892164</v>
+        <v>0.0001038175207891999</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001629743237248469</v>
+        <v>0.0001629743237248399</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001168603292298776</v>
+        <v>0.0001168603292298772</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001402002862809513</v>
+        <v>0.0001402002862809569</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001667190314160493</v>
+        <v>0.0001667190314160491</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001448957857776326</v>
+        <v>0.0001448957857776032</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000219093785586356</v>
+        <v>0.0002190937855863561</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002643896205281971</v>
+        <v>0.0002643896205281649</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001744315589173402</v>
+        <v>0.0001744315589173399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002681736731980147</v>
+        <v>0.0002681736731980143</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003124840161064563</v>
+        <v>0.0003124840161064323</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0005091815123602539</v>
+        <v>0.0005091815123602251</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003773818718031208</v>
+        <v>0.0003773818718030919</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004031173596105535</v>
+        <v>0.0004031173596105406</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005296365888805388</v>
+        <v>0.0005296365888805092</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004036434023439675</v>
+        <v>0.0004036434023439164</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0002806965123436233</v>
+        <v>0.0002806965123436218</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0003712437155542288</v>
+        <v>0.0003712437155542386</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004394359993960299</v>
+        <v>0.0004394359993959923</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003720092703465989</v>
+        <v>0.0003720092703465919</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002375796237049303</v>
+        <v>0.0002375796237049016</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004728211230910363</v>
+        <v>0.0004728211230910103</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003905685272340176</v>
+        <v>0.0003905685272339916</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004284198660080364</v>
+        <v>0.0004284198660080223</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003715103140365895</v>
+        <v>0.0003715103140365599</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0004343621403417543</v>
+        <v>0.0004343621403417544</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001191264613795075</v>
+        <v>0.001191264613795046</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00163947901109001</v>
+        <v>0.001639479011089977</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001003201669640532</v>
+        <v>0.0010032016696405</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0004143001750049875</v>
+        <v>0.0004143001750049535</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001066263447924566</v>
+        <v>0.001066263447924521</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0002137586228060955</v>
+        <v>0.0002137586228060954</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001323088656137839</v>
+        <v>0.0001323088656137461</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001842217878165849</v>
+        <v>0.0001842217878165848</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="E3" t="n">
         <v>0.0001531656872329582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001386825697625344</v>
+        <v>0.0001386825697625341</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001945276315625574</v>
+        <v>0.0001945276315625471</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001824482507670862</v>
+        <v>0.0001824482507670623</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001817614719630405</v>
+        <v>0.0001817614719630393</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000143895180983992</v>
+        <v>0.0001438951809839624</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000154872890995196</v>
+        <v>0.0001548728909951702</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001521819890178588</v>
+        <v>0.0001521819890178117</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001221814447508354</v>
+        <v>0.0001221814447508118</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001586627675480589</v>
+        <v>0.0001586627675480381</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001665074682868899</v>
+        <v>0.0001665074682868897</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0001838520451754134</v>
+        <v>0.0001838520451753859</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001269045513017845</v>
+        <v>0.0001269045513017329</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002350346300367393</v>
+        <v>0.0002350346300367254</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001313516127261098</v>
+        <v>0.0001313516127260734</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0001838419175448994</v>
+        <v>0.0001838419175448916</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002361730878107588</v>
+        <v>0.0002361730878107586</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001410252837473137</v>
+        <v>0.001410252837473107</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001437538549144805</v>
+        <v>0.001437538549144817</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001453806937072266</v>
+        <v>0.001453806937072228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001418961509556683</v>
+        <v>0.00141896150955669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001454134698297065</v>
+        <v>0.00145413469829707</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001471336779507637</v>
+        <v>0.001471336779507594</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001543030707153532</v>
+        <v>0.0015430307071535</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001494991285839974</v>
+        <v>0.001494991285839945</v>
       </c>
       <c r="J4" t="n">
         <v>0.001495113056568502</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001550486342349541</v>
+        <v>0.001550486342349511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001504563305343638</v>
+        <v>0.00150456330534361</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001458428460056682</v>
+        <v>0.001458428460056684</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001492753999965117</v>
+        <v>0.001492753999965108</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00151760928667123</v>
+        <v>0.001517609286671201</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001493033035697329</v>
+        <v>0.00149303303569732</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001444035008049063</v>
+        <v>0.001444035008049034</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001529777772230148</v>
+        <v>0.001529777772230116</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001499797666899008</v>
+        <v>0.001499797666898981</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001513594035409275</v>
+        <v>0.001513594035409258</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001492851171981386</v>
+        <v>0.001492851171981356</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001457852143030773</v>
+        <v>0.001457852143030775</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001791641988202373</v>
+        <v>0.001791641988202337</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00195501087281719</v>
+        <v>0.001955010872817164</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001723095253404618</v>
+        <v>0.001723095253404593</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001508447573840441</v>
+        <v>0.001508447573840419</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001746080531080356</v>
+        <v>0.001746080531080331</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001434399639318169</v>
+        <v>0.001434399639318172</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001405665052876473</v>
+        <v>0.001405665052876462</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001424828115445404</v>
+        <v>0.001424828115445407</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00141121034904421</v>
+        <v>0.001411210349044206</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001406936711656135</v>
+        <v>0.001406936711656145</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001428343062455176</v>
+        <v>0.001428343062455163</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001414681757622558</v>
+        <v>0.001414681757622557</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001422367799591864</v>
+        <v>0.001422367799591861</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001409888128775534</v>
+        <v>0.001409888128775518</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001413889375167864</v>
+        <v>0.001413889375167825</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001412908572995291</v>
+        <v>0.001412908572995245</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00140197372689411</v>
+        <v>0.0014019737268941</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001415270740668374</v>
+        <v>0.001415270740668369</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001360222260375133</v>
+        <v>0.001360222260375134</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001424451936576121</v>
+        <v>0.001424451936576104</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001403695243770427</v>
+        <v>0.001403695243770393</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001443107387741845</v>
+        <v>0.00144310738774181</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001405316145439542</v>
+        <v>0.001405316145439535</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001424448245173715</v>
+        <v>0.001424448245173714</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001442569448608425</v>
+        <v>0.001442569448608434</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.585964734880511e-05</v>
+        <v>9.585964734876894e-05</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001231453590204882</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001394137469479347</v>
+        <v>0.0001394137469479069</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001045683194323601</v>
+        <v>0.00010456831943236</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001397415081727421</v>
+        <v>0.0001397415081727418</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001464375395237041</v>
+        <v>0.0001464375395236642</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002286375170291994</v>
+        <v>0.0002286375170291637</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001805980957156426</v>
+        <v>0.0001805980957156061</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001790027084777388</v>
+        <v>0.000179002708477731</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002360931522252073</v>
+        <v>0.0002360931522251719</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001901701152193103</v>
+        <v>0.0001901701152192975</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001440352699323572</v>
+        <v>0.0001440352699323525</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001783608098407952</v>
+        <v>0.0001783608098407691</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001927100466873016</v>
+        <v>0.0001927100466872743</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001681337957133971</v>
+        <v>0.0001681337957133924</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000129641817924732</v>
+        <v>0.0001296418179246962</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002153845821058163</v>
+        <v>0.0002153845821057767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001854044767746818</v>
+        <v>0.0001854044767746432</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001992008452849438</v>
+        <v>0.0001992008452849171</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001679519319974538</v>
+        <v>0.000167951931997426</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001894506618933502</v>
+        <v>0.0001894506618933504</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00046674274821844</v>
+        <v>0.0004667427482184083</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0006301116328332573</v>
+        <v>0.0006301116328332299</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0004087020632802893</v>
+        <v>0.0004087020632802578</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001940543837161078</v>
+        <v>0.0001940543837160815</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.000431687340956021</v>
+        <v>0.0004316873409560092</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001200064491938443</v>
+        <v>0.0001200064491938442</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.127186275214195e-05</v>
+        <v>9.127186275211926e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001104349253210786</v>
+        <v>0.0001104349253210785</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="E7" t="n">
-        <v>9.681715891987599e-05</v>
+        <v>9.681715891987588e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>9.254352153181597e-05</v>
+        <v>9.254352153181577e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001034438224712488</v>
+        <v>0.0001034438224712318</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="J7" t="n">
-        <v>9.857140953180954e-05</v>
+        <v>9.857140953178384e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001079746094675334</v>
+        <v>0.0001079746094675288</v>
       </c>
       <c r="N7" t="n">
-        <v>9.549493865121463e-05</v>
+        <v>9.549493865118098e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>8.89901351839321e-05</v>
+        <v>8.899013518389538e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>8.800933301135865e-05</v>
+        <v>8.800933301131513e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.758053676978584e-05</v>
+        <v>8.758053676976141e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="U7" t="n">
-        <v>9.037150068444295e-05</v>
+        <v>9.037150068443916e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>9.182077923771125e-05</v>
+        <v>9.182077923771109e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>9.955269659219332e-05</v>
+        <v>9.955269659217626e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>7.879600378650266e-05</v>
+        <v>7.879600378646399e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001287141976175183</v>
+        <v>0.0001287141976174679</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.092295531522013e-05</v>
+        <v>9.092295531519633e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001100550550493895</v>
+        <v>0.0001100550550493766</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001281762584841076</v>
+        <v>0.0001281762584841074</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001140559682650504</v>
+        <v>0.001140559682650534</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000398672709594072</v>
+        <v>0.000398672709594078</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001195683085469745</v>
+        <v>0.001195683085469748</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005267224022462232</v>
+        <v>0.0005267224022462362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000668404771497649</v>
+        <v>0.0006684047714976516</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001212458344434705</v>
+        <v>0.001212458344434703</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001637990875190127</v>
+        <v>0.00163799087519013</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001206430468548227</v>
+        <v>0.00120643046854823</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001380568467952572</v>
+        <v>0.001380568467952563</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002174438008482256</v>
+        <v>0.002174438008482258</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001314321704047914</v>
+        <v>0.001314321704048014</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003818674184573029</v>
+        <v>0.00381867418457303</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001355270173402706</v>
+        <v>0.001355270173402709</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001044786032703391</v>
+        <v>0.001044786032703395</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001148368931855201</v>
+        <v>0.001148368931855206</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0007692432647830347</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001393324918477812</v>
+        <v>0.001393324918477816</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001242868029851665</v>
+        <v>0.001242868029851675</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001543829857842052</v>
+        <v>0.001543829857842055</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001810797617957127</v>
+        <v>0.001810797617957129</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0005856755503346281</v>
+        <v>0.0005856755503346242</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002193399609396479</v>
+        <v>0.002193399609396481</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001241738703306334</v>
+        <v>0.001241738703306321</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001283742047899573</v>
+        <v>0.001283742047899579</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0008092974586286082</v>
+        <v>0.0008092974586286152</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001717581086779192</v>
+        <v>0.001717581086779203</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.002242282171076278</v>
+        <v>0.002242282171076308</v>
       </c>
     </row>
     <row r="3">
@@ -2042,82 +2042,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001581600422987493</v>
+        <v>0.0001581600422987412</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002168140178141497</v>
+        <v>0.0002168140178141452</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001808137933461617</v>
+        <v>0.0001808137933461621</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001646895427816928</v>
+        <v>0.0001646895427816933</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002304656205454086</v>
+        <v>0.0002304656205454059</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002159391738065471</v>
+        <v>0.0002159391738065486</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000223368816682103</v>
+        <v>0.0002233688166821037</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001716247136080716</v>
+        <v>0.0001716247136080717</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001843821133800831</v>
+        <v>0.0001843821133800683</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001812549664391456</v>
+        <v>0.0001812549664391452</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001463907792686491</v>
+        <v>0.0001463907792686376</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001887932319506259</v>
+        <v>0.0001887932319506182</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001957851252415209</v>
+        <v>0.0001957851252415271</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002180593242400237</v>
+        <v>0.000218059324240024</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001518795887227992</v>
+        <v>0.0001518795887227985</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002775512415989962</v>
+        <v>0.000277551241598985</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001570476010184326</v>
+        <v>0.0001570476010184259</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002180475547208423</v>
+        <v>0.0002180475547208428</v>
       </c>
       <c r="AB3" t="n">
         <v>0.0002836425015521158</v>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001843356444025163</v>
+        <v>0.001843356444025162</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001572163426833641</v>
+        <v>0.001572163426833638</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0018634482770611</v>
+        <v>0.001863448277061099</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001616222881349683</v>
+        <v>0.001616222881349685</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001669481916209184</v>
+        <v>0.001669481916209182</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001869562661968792</v>
+        <v>0.001869562661968793</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002024664272573886</v>
+        <v>0.002024664272573887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001867365571991063</v>
+        <v>0.001867365571991062</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001913728764043174</v>
+        <v>0.00191372876404317</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002220192953378591</v>
+        <v>0.002220192953378592</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001906690660407846</v>
+        <v>0.001906690660407843</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00282287945642949</v>
+        <v>0.002822879456429492</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001921615896646465</v>
+        <v>0.001921615896646468</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001808448073250421</v>
+        <v>0.00180844807325042</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001846202823659441</v>
+        <v>0.001846202823659446</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001708015969929986</v>
+        <v>0.00170801596992999</v>
       </c>
       <c r="R4" t="n">
         <v>0.001935486404364963</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001880646635214717</v>
+        <v>0.001880646635214718</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001990343687445002</v>
+        <v>0.001990343687445</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002087650301113235</v>
+        <v>0.002087650301113236</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001532177628283485</v>
+        <v>0.001532177628283494</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002227104234253466</v>
+        <v>0.002227104234253467</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001880235008950169</v>
+        <v>0.001880235008950178</v>
       </c>
       <c r="Y4" t="n">
         <v>0.001895544734826229</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00172261525324661</v>
+        <v>0.001722615253246606</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00205367397010265</v>
+        <v>0.002053673970102654</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002246851677987924</v>
+        <v>0.002246851677987929</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00148528331103595</v>
+        <v>0.001485283311035949</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001505878069172434</v>
+        <v>0.001505878069172422</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001490143255269573</v>
+        <v>0.001490143255269571</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001485883630265066</v>
+        <v>0.001485883630265063</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001511637845251891</v>
+        <v>0.001511637845251887</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001489235062094582</v>
+        <v>0.001489235062094579</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001512432868040384</v>
+        <v>0.001512432868040379</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001490191025618043</v>
+        <v>0.00149019102561804</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001494840948029991</v>
+        <v>0.001494840948029985</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001493701139690834</v>
+        <v>0.001493701139690828</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001480993552863141</v>
+        <v>0.001480993552863144</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001496448748950982</v>
+        <v>0.001496448748950975</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00139006714666157</v>
+        <v>0.001390067146661566</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001507115895930663</v>
+        <v>0.001507115895930662</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001482994159456325</v>
+        <v>0.001482994159456328</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001528800001218643</v>
+        <v>0.001528800001218632</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00148487783925222</v>
+        <v>0.001484877839252214</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001507111606079127</v>
+        <v>0.001507111606079117</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001532950517954563</v>
+        <v>0.001532950517954562</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0004671118421023874</v>
+        <v>0.0004671118421023911</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001959188249108652</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004872036751383251</v>
+        <v>0.0004872036751383204</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002399782794269083</v>
+        <v>0.0002399782794269127</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002932373142864088</v>
+        <v>0.00029323731428641</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004825402587033006</v>
+        <v>0.0004825402587033012</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0006484196706511108</v>
+        <v>0.0006484196706511074</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004911209700682873</v>
+        <v>0.0004911209700682836</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005429078183678171</v>
+        <v>0.000542907818367813</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008439483514558128</v>
+        <v>0.0008439483514558097</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005304460584850699</v>
+        <v>0.0005304460584850666</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001446634854506713</v>
+        <v>0.001446634854506711</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00054537129472369</v>
+        <v>0.000545371294723687</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0004214256699849274</v>
+        <v>0.0004214256699849275</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00045918042039395</v>
+        <v>0.0004591804203939536</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0003317713680072115</v>
+        <v>0.0003317713680072066</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0005592418024421881</v>
+        <v>0.0005592418024421848</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0005044020332919432</v>
+        <v>0.0005044020332919404</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0006140990855222261</v>
+        <v>0.0006140990855222229</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000700627897847743</v>
+        <v>0.0007006278978477459</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002510254980939762</v>
+        <v>0.0002510254980939712</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0008400818309879749</v>
+        <v>0.0008400818309879786</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0004932126056846761</v>
+        <v>0.0004932126056846815</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0005193001329034541</v>
+        <v>0.0005193001329034501</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0003463706513238321</v>
+        <v>0.0003463706513238358</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006774293681798753</v>
+        <v>0.0006774293681798747</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008706070760651505</v>
+        <v>0.0008706070760651555</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000109038709113174</v>
+        <v>0.0001090387091131652</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001296334672496586</v>
+        <v>0.0001296334672496424</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001138986533467966</v>
+        <v>0.0001138986533467969</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001096390283422899</v>
+        <v>0.0001096390283422902</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001246154419863981</v>
+        <v>0.0001246154419863978</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001184141164192233</v>
+        <v>0.0001184141164192202</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001361882661176069</v>
+        <v>0.0001361882661176074</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001139464236952685</v>
+        <v>0.0001139464236952629</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001078185447644997</v>
+        <v>0.000107818544764491</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001066787364253416</v>
+        <v>0.0001066787364253377</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001047489509403662</v>
+        <v>0.0001047489509403562</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001094263456854923</v>
+        <v>0.0001094263456854878</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001089150164720596</v>
+        <v>0.0001089150164720663</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001200934926651711</v>
+        <v>0.0001200934926651738</v>
       </c>
       <c r="X7" t="n">
-        <v>9.597175619083408e-05</v>
+        <v>9.597175619083851e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001525553992958695</v>
+        <v>0.0001525553992958632</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001086332373294447</v>
+        <v>0.0001086332373294422</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001308670041563518</v>
+        <v>0.000130867004156355</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001567059160317881</v>
+        <v>0.0001567059160317885</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008989929246224704</v>
+        <v>0.0008989929246224754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003661717317255166</v>
+        <v>0.0003661717317255167</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001380989605336872</v>
+        <v>0.001380989605336873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005637211881502272</v>
+        <v>0.0005637211881502267</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005881008877801229</v>
+        <v>0.0005881008877801242</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001142273887585457</v>
+        <v>0.001142273887585458</v>
       </c>
       <c r="H2" t="n">
         <v>0.001442661127863953</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00142201266811986</v>
+        <v>0.001422012668119857</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00132333523394213</v>
+        <v>0.001323335233942131</v>
       </c>
       <c r="K2" t="n">
         <v>0.001482655754060499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001085699580836462</v>
+        <v>0.00108569958083646</v>
       </c>
       <c r="M2" t="n">
         <v>0.003321876002424981</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0009334650389533854</v>
+        <v>0.0009334650389533832</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0008012157351830683</v>
+        <v>0.0008012157351830659</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00109306589310875</v>
+        <v>0.001093065893108749</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0006167482990684588</v>
+        <v>0.0006167482990684602</v>
       </c>
       <c r="R2" t="n">
         <v>0.001168282419534183</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001137003128678883</v>
+        <v>0.001137003128678882</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001299247953364293</v>
+        <v>0.001299247953364292</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001397579250768239</v>
+        <v>0.001397579250768237</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0006938990792867937</v>
+        <v>0.0006938990792868001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002049014932175556</v>
+        <v>0.002049014932175548</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001749452102623281</v>
+        <v>0.00174945210262328</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001950206761395743</v>
+        <v>0.001950206761395746</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0008034255974482385</v>
+        <v>0.000803425597448236</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001729109353673817</v>
+        <v>0.001729109353673815</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.002081887906197062</v>
+        <v>0.002081887906197055</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001543494455410727</v>
+        <v>0.0001543494455410763</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002112755407199174</v>
+        <v>0.0002112755407199175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001765046840505939</v>
+        <v>0.0001765046840505942</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001604817580080093</v>
+        <v>0.0001604817580080092</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002245794018563056</v>
+        <v>0.0002245794018563088</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002105248767267801</v>
+        <v>0.0002105248767267861</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002166154322661338</v>
+        <v>0.0002166154322661339</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001674275966428611</v>
+        <v>0.0001674275966428643</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001798187793196244</v>
+        <v>0.0001798187793196329</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001767814010377715</v>
+        <v>0.0001767814010377733</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001429180339064987</v>
+        <v>0.0001429180339065043</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001840968999843113</v>
+        <v>0.0001840968999843236</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001911611537244612</v>
+        <v>0.0001911611537244678</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002125292437791915</v>
+        <v>0.0002125292437791948</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001482492802283372</v>
+        <v>0.0001482492802283446</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002703024720134841</v>
+        <v>0.0002703024720134784</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001532689382774082</v>
+        <v>0.0001532689382774069</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002125178121212486</v>
+        <v>0.0002125178121212489</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002758927482920478</v>
+        <v>0.0002758927482920446</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001751453665572961</v>
+        <v>0.001751453665572962</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00155645711940132</v>
+        <v>0.001556457119401322</v>
       </c>
       <c r="D4" t="n">
         <v>0.001927135795802579</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001626047955455485</v>
+        <v>0.001626047955455487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001636275348704118</v>
+        <v>0.001636275348704121</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001840126719823671</v>
+        <v>0.001840126719823668</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001949614341580119</v>
+        <v>0.001949614341580117</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001942088220469852</v>
+        <v>0.001942088220469851</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001892317321404805</v>
+        <v>0.001892317321404811</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001964191913188146</v>
+        <v>0.001964191913188144</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001819506049342711</v>
+        <v>0.001819506049342709</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002637170182221195</v>
+        <v>0.002637170182221193</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001764018346454572</v>
+        <v>0.001764018346454571</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001715815028180024</v>
+        <v>0.00171581502818002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001822190983666354</v>
+        <v>0.001822190983666352</v>
       </c>
       <c r="Q4" t="n">
         <v>0.001648578813842245</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001849606524311377</v>
+        <v>0.001849606524311375</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001838205590094597</v>
+        <v>0.001838205590094594</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001897341923517507</v>
+        <v>0.001897341923517509</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001933182526756856</v>
+        <v>0.001933182526756855</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00158960381236332</v>
+        <v>0.001589603812363339</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002170623183085846</v>
+        <v>0.002170623183085843</v>
       </c>
       <c r="X4" t="n">
         <v>0.002061436049358382</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002134608765100725</v>
+        <v>0.002134608765100724</v>
       </c>
       <c r="Z4" t="n">
         <v>0.001716620497026164</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002054021356242924</v>
+        <v>0.002054021356242921</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002184265723908652</v>
+        <v>0.002184265723908644</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001480039861492987</v>
+        <v>0.00148003986149299</v>
       </c>
       <c r="C5" t="n">
         <v>0.001499999276662683</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001484912086636928</v>
+        <v>0.001484912086636926</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001480413197259519</v>
+        <v>0.001480413197259522</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001505637855888105</v>
+        <v>0.001505637855888112</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001486711013478764</v>
+        <v>0.001486711013478766</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001505339168208888</v>
+        <v>0.001505339168208891</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001484806693998186</v>
+        <v>0.001484806693998193</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001489323134579258</v>
+        <v>0.001489323134579261</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001488216045862213</v>
+        <v>0.001488216045862214</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001475873246186598</v>
+        <v>0.0014758732461866</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001490882459325302</v>
+        <v>0.001490882459325307</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001406361741942625</v>
+        <v>0.001406361741942621</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001501245714769099</v>
+        <v>0.001501245714769106</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001477816422868256</v>
+        <v>0.001477816422868261</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001522303378053</v>
+        <v>0.001522303378052999</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001479646029283341</v>
+        <v>0.001479646029283342</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001501241548064016</v>
+        <v>0.001501241548064021</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001526001695918121</v>
+        <v>0.001526001695918113</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0003782842239763034</v>
+        <v>0.0003782842239763014</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001832876778046643</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005539663542059202</v>
+        <v>0.0005539663542059189</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002528785138588311</v>
+        <v>0.0002528785138588309</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002631059071074616</v>
+        <v>0.0002631059071074623</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004562566488131239</v>
+        <v>0.0004562566488131205</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005764448999834621</v>
+        <v>0.0005764448999834602</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005689187788731958</v>
+        <v>0.0005689187788731934</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005214111232361674</v>
+        <v>0.0005214111232361735</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0005910224715914907</v>
+        <v>0.0005910224715914889</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004463366077460541</v>
+        <v>0.0004463366077460528</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001264000740624542</v>
+        <v>0.001264000740624543</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0003908489048579161</v>
+        <v>0.0003908489048579141</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003319449571694779</v>
+        <v>0.0003319449571694752</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0004383209126558102</v>
+        <v>0.0004383209126558059</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002754093722455889</v>
+        <v>0.0002754093722455879</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004764370827147241</v>
+        <v>0.000476437082714719</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004650361484979413</v>
+        <v>0.0004650361484979391</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000524172481920854</v>
+        <v>0.0005241724819208526</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000549312455746311</v>
+        <v>0.0005493124557463088</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002900358923974157</v>
+        <v>0.0002900358923974227</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0007867531120753003</v>
+        <v>0.0007867531120752958</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0006775659783478396</v>
+        <v>0.0006775659783478349</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0007614393235040663</v>
+        <v>0.0007614393235040662</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0003434510554295085</v>
+        <v>0.000343451055429505</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006808519146462664</v>
+        <v>0.0006808519146462642</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008110962823119915</v>
+        <v>0.0008110962823119894</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001068704198963342</v>
+        <v>0.0001068704198963317</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001268298350660295</v>
+        <v>0.0001268298350660296</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001117426450402703</v>
+        <v>0.0001117426450402704</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001072437556628654</v>
+        <v>0.0001072437556628655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000121767784877559</v>
+        <v>0.000121767784877566</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001158048153101321</v>
+        <v>0.0001158048153101329</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001321697266122328</v>
+        <v>0.0001321697266122329</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001116372524015298</v>
+        <v>0.0001116372524015366</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001054530635687122</v>
+        <v>0.0001054530635687145</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001043459748516682</v>
+        <v>0.0001043459748516673</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001027038045899437</v>
+        <v>0.0001027038045899433</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001070123883147572</v>
+        <v>0.0001070123883147595</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001067938219767195</v>
+        <v>0.000106793821976722</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001173756437585536</v>
+        <v>0.00011737564375856</v>
       </c>
       <c r="X7" t="n">
-        <v>9.394635185771055e-05</v>
+        <v>9.394635185771434e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001491339364563441</v>
+        <v>0.0001491339364563416</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001064765876866841</v>
+        <v>0.000106476587686685</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001280721064673583</v>
+        <v>0.0001280721064673647</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001528322543214593</v>
+        <v>0.0001528322543214577</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007864501702086418</v>
+        <v>0.0007864501702086314</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003445447340891495</v>
+        <v>0.0003445447340891494</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009483018204528077</v>
+        <v>0.0009483018204527976</v>
       </c>
       <c r="E2" t="n">
         <v>0.000405419185923796</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0006681630973155916</v>
+        <v>0.0006681630973155922</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001035275824415714</v>
+        <v>0.001035275824415706</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001336963263071849</v>
+        <v>0.001336963263071836</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001280920025986827</v>
+        <v>0.001280920025986815</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001251219394807744</v>
+        <v>0.001251219394807737</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001722320768972458</v>
+        <v>0.001722320768972449</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009661348573546042</v>
+        <v>0.0009661348573545967</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002775304284634112</v>
+        <v>0.002775304284634127</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0006796254961011468</v>
+        <v>0.0006796254961011352</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0007769149478630638</v>
+        <v>0.0007769149478630514</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0009854298254895841</v>
+        <v>0.0009854298254895772</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0006093393681548994</v>
+        <v>0.0006093393681548869</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001226818035058022</v>
+        <v>0.001226818035058011</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001063869100934799</v>
+        <v>0.001063869100934789</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001353463424699121</v>
+        <v>0.001353463424699109</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001456185302535859</v>
+        <v>0.001456185302535846</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000943302061079062</v>
+        <v>0.0009433020610790597</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001786699438626102</v>
+        <v>0.001786699438626089</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00194440313932011</v>
+        <v>0.001944403139320101</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.002809166893967339</v>
+        <v>0.002809166893967337</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0006868450937755593</v>
+        <v>0.0006868450937755553</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001757691926986588</v>
+        <v>0.001757691926986576</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001898265353631274</v>
+        <v>0.001898265353631275</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001518264390638561</v>
+        <v>0.00015182643906385</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002082257586169049</v>
+        <v>0.000208225758616905</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001737797320720229</v>
+        <v>0.0001737797320720228</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001585614817009983</v>
+        <v>0.0001585614817009982</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002209874546180252</v>
+        <v>0.0002209874546180114</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002074625147932247</v>
+        <v>0.0002074625147932235</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002121465165130453</v>
+        <v>0.0002121465165130591</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001647055331030421</v>
+        <v>0.0001647055331030376</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001769081147757602</v>
+        <v>0.000176908114775748</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001739169671572198</v>
+        <v>0.0001739169671572055</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001405690201599548</v>
+        <v>0.0001405690201599497</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001811211748663754</v>
+        <v>0.0001811211748663647</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001889740791241946</v>
+        <v>0.0001889740791241917</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000209120706950769</v>
+        <v>0.00020912070695076</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001458191218129337</v>
+        <v>0.0001458191218129303</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002660146870013935</v>
+        <v>0.0002660146870013858</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001507623777489786</v>
+        <v>0.0001507623777489673</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002091094492904315</v>
+        <v>0.0002091094492904195</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002714090472093696</v>
+        <v>0.0002714090472093697</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001701660224626939</v>
+        <v>0.001701660224626931</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001540029286477161</v>
+        <v>0.001540029286477159</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001760653250582906</v>
+        <v>0.001760653250582898</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001559710524786698</v>
+        <v>0.001559710524786697</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00165715485250997</v>
+        <v>0.001657154852509967</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001792354253727065</v>
+        <v>0.001792354253727059</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001902315782524465</v>
+        <v>0.001902315782524456</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001881888680699888</v>
+        <v>0.001881888680699879</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001860889515011201</v>
+        <v>0.001860889515011196</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002042774068328943</v>
+        <v>0.002042774068328933</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001767153183127515</v>
+        <v>0.00176715318312751</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002428504286913906</v>
+        <v>0.002428504286913916</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001662723885313412</v>
+        <v>0.001662723885313403</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001698184748050211</v>
+        <v>0.001698184748050202</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001774185972439764</v>
+        <v>0.001774185972439757</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001637105417018389</v>
+        <v>0.001637105417018379</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001862169140303992</v>
+        <v>0.001862169140303984</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001802776167259076</v>
+        <v>0.001802776167259063</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001908329897682928</v>
+        <v>0.001908329897682918</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001945770815933227</v>
+        <v>0.001945770815933218</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001695112082870594</v>
+        <v>0.001695112082870602</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002066239337445186</v>
+        <v>0.002066239337445177</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002123720484497802</v>
+        <v>0.002123720484497796</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00243891671849803</v>
+        <v>0.002438916718498026</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001665355343888943</v>
+        <v>0.001665355343888933</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002055666440075983</v>
+        <v>0.002055666440075974</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002108468880637353</v>
+        <v>0.002108468880637352</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001470347326752762</v>
+        <v>0.001470347326752751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001490342620655755</v>
+        <v>0.001490342620655753</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001475280663905526</v>
+        <v>0.001475280663905524</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001471411047662741</v>
+        <v>0.00147141104766274</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001495555704792608</v>
+        <v>0.001495555704792595</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001480452388657995</v>
+        <v>0.001480452388657991</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001494263378551879</v>
+        <v>0.001494263378551891</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00147504160529609</v>
+        <v>0.001475041605296077</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001479489303025841</v>
+        <v>0.001479489303025831</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001478399064842708</v>
+        <v>0.001478399064842701</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001466244129753578</v>
+        <v>0.001466244129753565</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001481024913956624</v>
+        <v>0.001481024913956611</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001420168391214414</v>
+        <v>0.001420168391214427</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001491230414614279</v>
+        <v>0.001491230414614268</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001468157730156277</v>
+        <v>0.001468157730156271</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001511967602259884</v>
+        <v>0.001511967602259877</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001469959488898327</v>
+        <v>0.001469959488898314</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001491226311329277</v>
+        <v>0.001491226311329269</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001515498860457815</v>
+        <v>0.001515498860457814</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0003365065507048729</v>
+        <v>0.000336506550704862</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001748756125550916</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0003954995766608389</v>
+        <v>0.0003954995766608293</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001945568508646302</v>
+        <v>0.0001945568508646304</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002920011785879001</v>
+        <v>0.0002920011785878999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004165392391506322</v>
+        <v>0.0004165392391506165</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005371621086023989</v>
+        <v>0.000537162108602388</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005167350067778234</v>
+        <v>0.0005167350067778129</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004946236656742221</v>
+        <v>0.0004946236656742176</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0006776203944068734</v>
+        <v>0.0006776203944068645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004019995092054507</v>
+        <v>0.0004019995092054422</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001063350612991834</v>
+        <v>0.001063350612991831</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002975702113913465</v>
+        <v>0.0002975702113913361</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003223697334737699</v>
+        <v>0.0003223697334737576</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0003983709578633246</v>
+        <v>0.0003983709578633142</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002719517430963223</v>
+        <v>0.0002719517430963122</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004970154663819267</v>
+        <v>0.0004970154663819161</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004376224933370076</v>
+        <v>0.0004376224933369933</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005431762237608607</v>
+        <v>0.0005431762237608499</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005699558013567884</v>
+        <v>0.000569955801356776</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0003808357342323298</v>
+        <v>0.0003808357342323284</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000690424322868747</v>
+        <v>0.0006904243228687345</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0007479054699213567</v>
+        <v>0.0007479054699213529</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001073763044575963</v>
+        <v>0.001073763044575956</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0003002016699668789</v>
+        <v>0.000300201669966866</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006905127661539168</v>
+        <v>0.0006905127661539062</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0007433152067152824</v>
+        <v>0.0007433152067152826</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001051936528306855</v>
+        <v>0.000105193652830683</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001251889467336863</v>
+        <v>0.0001251889467336862</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001101269899834558</v>
+        <v>0.0001101269899834556</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001062573737406735</v>
+        <v>0.0001062573737406733</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001197406902161588</v>
+        <v>0.0001197406902161524</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001141865393210124</v>
+        <v>0.0001141865393210104</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000129109704629808</v>
+        <v>0.0001291097046298019</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001098879313740141</v>
+        <v>0.0001098879313740092</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001036742884493988</v>
+        <v>0.0001036742884493887</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001025840502662682</v>
+        <v>0.0001025840502662585</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001010904558315058</v>
+        <v>0.0001010904558314982</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001052098993801861</v>
+        <v>0.0001052098993801691</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001058920425761514</v>
+        <v>0.0001058920425761522</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001154154000378339</v>
+        <v>0.0001154154000378257</v>
       </c>
       <c r="X7" t="n">
-        <v>9.234271557983888e-05</v>
+        <v>9.234271557982835e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001468139283378205</v>
+        <v>0.00014681392833781</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001048058149762585</v>
+        <v>0.000104805814976247</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001260726374072138</v>
+        <v>0.0001260726374072007</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001503451865357443</v>
+        <v>0.0001503451865357442</v>
       </c>
     </row>
   </sheetData>
@@ -4006,82 +4006,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0003253597202835179</v>
+        <v>0.0003253597202835181</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001469634147957783</v>
+        <v>0.0001469634147957781</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0006967757331309064</v>
+        <v>0.0006967757331309068</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003548259370856316</v>
+        <v>0.0003548259370856319</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002979132780762991</v>
+        <v>0.0002979132780762993</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004543461430307768</v>
+        <v>0.0004543461430307775</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008685150779771106</v>
+        <v>0.0008685150779771105</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007383226974937153</v>
+        <v>0.0007383226974937155</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0006321489432038404</v>
+        <v>0.0006321489432038402</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001047471686332722</v>
+        <v>0.001047471686332723</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007676334591131529</v>
+        <v>0.000767633459113153</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001338031598759109</v>
+        <v>0.001338031598759108</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008628290080150785</v>
+        <v>0.000862829008015078</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0003978585783233144</v>
+        <v>0.0003978585783233151</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005763347094880978</v>
+        <v>0.000576334709488099</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005449262067586499</v>
+        <v>0.0005449262067586496</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007336539556442832</v>
+        <v>0.0007336539556442833</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006034171611417125</v>
+        <v>0.0006034171611417132</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0005617230039739815</v>
+        <v>0.0005617230039739821</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009145588574495529</v>
+        <v>0.000914558857449555</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0003295055356074392</v>
+        <v>0.0003295055356074382</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001822246077748132</v>
+        <v>0.001822246077748134</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007914304280740179</v>
+        <v>0.0007914304280740194</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.000414497993614787</v>
+        <v>0.0004144979936147869</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0005459967722504704</v>
+        <v>0.0005459967722504712</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001113019073229153</v>
+        <v>0.001113019073229152</v>
       </c>
       <c r="AB2" t="n">
         <v>0.00115219612945295</v>
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001383758785389727</v>
+        <v>0.0001383758785389747</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001917079628690131</v>
+        <v>0.000191707962869013</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001598081433552373</v>
+        <v>0.0001598081433552374</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001445196586632376</v>
+        <v>0.0001445196586632375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002032007399899896</v>
+        <v>0.0002032007399899924</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001903863352928219</v>
+        <v>0.0001903863352928221</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001922609885932194</v>
+        <v>0.0001922609885932195</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001504474983660086</v>
+        <v>0.0001504474983660094</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001618850207879645</v>
+        <v>0.0001618850207879657</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001590814076781651</v>
+        <v>0.0001590814076781665</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001278242604806898</v>
+        <v>0.0001278242604806902</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001658285676798877</v>
+        <v>0.0001658285676798878</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001731419980025848</v>
+        <v>0.0001731419980025835</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000192077995947462</v>
+        <v>0.0001920779959474636</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001327451990949992</v>
+        <v>0.0001327451990949996</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002453957372995418</v>
+        <v>0.0002453957372995413</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001373785301523237</v>
+        <v>0.0001373785301523243</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0001920674441081441</v>
+        <v>0.0001920674441081456</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002492386003963227</v>
+        <v>0.0002492386003963222</v>
       </c>
     </row>
     <row r="4">
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001487949816733006</v>
+        <v>0.001487949816733007</v>
       </c>
       <c r="C4" t="n">
         <v>0.001422698003669199</v>
@@ -4197,25 +4197,25 @@
         <v>0.001476534605589894</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001534963853189337</v>
+        <v>0.001534963853189336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001685923566560096</v>
+        <v>0.0016859235665601</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001638469972670015</v>
+        <v>0.00163846997267002</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001586636209662568</v>
+        <v>0.00158663620966257</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001751151148891126</v>
+        <v>0.001751151148891128</v>
       </c>
       <c r="L4" t="n">
         <v>0.001649153401095961</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00185717982483677</v>
+        <v>0.001857179824836769</v>
       </c>
       <c r="N4" t="n">
         <v>0.001683851060828141</v>
@@ -4227,34 +4227,34 @@
         <v>0.00157942725320096</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001567979222773335</v>
+        <v>0.001567979222773337</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001636768271089032</v>
+        <v>0.001636768271089033</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001589298488810501</v>
+        <v>0.001589298488810502</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001574101458120374</v>
+        <v>0.001574101458120375</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001702705983504447</v>
+        <v>0.001702705983504448</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001406279257259298</v>
+        <v>0.001406279257259297</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002033547316701808</v>
+        <v>0.002033547316701807</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001657827116844079</v>
+        <v>0.00165782711684408</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001520439670647802</v>
+        <v>0.001520439670647803</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00156836943132389</v>
+        <v>0.001568369431323892</v>
       </c>
       <c r="AA4" t="n">
         <v>0.001775042401718598</v>
@@ -4270,61 +4270,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001419796402092242</v>
+        <v>0.001419796402092245</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001439006866024883</v>
+        <v>0.001439006866024884</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001425275802835591</v>
+        <v>0.001425275802835592</v>
       </c>
       <c r="F5" t="n">
         <v>0.001420624432552653</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001443424302879185</v>
+        <v>0.001443424302879188</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="J5" t="n">
         <v>0.001425618926517445</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001439559891749086</v>
+        <v>0.001439559891749087</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001424196365767082</v>
+        <v>0.001424196365767083</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001428365208383717</v>
+        <v>0.001428365208383719</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001427343324326881</v>
+        <v>0.001427343324326882</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001415950461213355</v>
+        <v>0.001415950461213357</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="U5" t="n">
         <v>0.001429802584918357</v>
@@ -4333,22 +4333,22 @@
         <v>0.00134928658391569</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001439370193285538</v>
+        <v>0.001439370193285537</v>
       </c>
       <c r="X5" t="n">
         <v>0.001417744085553692</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001458803883919843</v>
+        <v>0.001458803883919845</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001419432880316766</v>
+        <v>0.00141943288031677</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001439366347264013</v>
+        <v>0.001439366347264012</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001460894617899298</v>
+        <v>0.001460894617899299</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001634612338530293</v>
+        <v>0.000163461233853029</v>
       </c>
       <c r="C6" t="n">
         <v>9.820942078922159e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002988380091488827</v>
+        <v>0.0002988380091488821</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001718689157557896</v>
+        <v>0.0001718689157557895</v>
       </c>
       <c r="F6" t="n">
         <v>0.0001520460227099165</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001998413443828945</v>
+        <v>0.0001998413443828934</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003614349836801199</v>
+        <v>0.0003614349836801224</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003139813897900387</v>
+        <v>0.0003139813897900412</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002640074912234914</v>
+        <v>0.0002640074912234928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0004266625660111488</v>
+        <v>0.000426662566011149</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003246648182159843</v>
+        <v>0.0003246648182159834</v>
       </c>
       <c r="M6" t="n">
         <v>0.0005326912419567916</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0003593624779481637</v>
+        <v>0.0003593624779481633</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001792522903574984</v>
+        <v>0.0001792522903574986</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002443047443945198</v>
+        <v>0.000244304744394519</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002434906398933586</v>
+        <v>0.0002434906398933589</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003122796882090557</v>
+        <v>0.0003122796882090556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002648099059305218</v>
+        <v>0.0002648099059305221</v>
       </c>
       <c r="T6" t="n">
         <v>0.0002496128752403961</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0003675834746980049</v>
+        <v>0.0003675834746980045</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001523201973833928</v>
+        <v>0.0001523201973833926</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0006984248078953676</v>
+        <v>0.0006984248078953661</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0003227046080376378</v>
+        <v>0.0003227046080376381</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001959510877678244</v>
+        <v>0.0001959510877678249</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002438808484439125</v>
+        <v>0.0002438808484439123</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0004505538188386208</v>
+        <v>0.0004505538188386198</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0004655234512978288</v>
+        <v>0.0004655234512978284</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.530781921226825e-05</v>
+        <v>9.53078192122702e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0.000114518283144905</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000100787219955613</v>
+        <v>0.0001007872199556129</v>
       </c>
       <c r="F7" t="n">
-        <v>9.613584967267517e-05</v>
+        <v>9.613584967267522e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001083017940727437</v>
+        <v>0.0001083017940727458</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001029902080783703</v>
+        <v>0.0001029902080783699</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="M7" t="n">
         <v>0.000115071308869109</v>
       </c>
       <c r="N7" t="n">
-        <v>9.970778288710505e-05</v>
+        <v>9.970778288710429e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>9.324269957727422e-05</v>
+        <v>9.324269957727632e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>9.222081552043976e-05</v>
+        <v>9.22208155204406e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.146187833337768e-05</v>
+        <v>9.146187833337863e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="U7" t="n">
-        <v>9.468007611191468e-05</v>
+        <v>9.468007611191439e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>9.532752403978336e-05</v>
+        <v>9.532752403978283e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001042476844790972</v>
+        <v>0.0001042476844790967</v>
       </c>
       <c r="X7" t="n">
-        <v>8.262157674725128e-05</v>
+        <v>8.26215767472496e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001343153010398654</v>
+        <v>0.0001343153010398674</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.494429743678919e-05</v>
+        <v>9.494429743679085e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001148777643840363</v>
+        <v>0.0001148777643840356</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001364060350193203</v>
+        <v>0.0001364060350193204</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002034318443902738</v>
+        <v>0.0002034318443902682</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002424128231984652</v>
+        <v>0.0002424128231984667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002828100672267012</v>
+        <v>0.0002828100672266961</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002837967945273832</v>
+        <v>0.0002837967945273829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0003134750816873721</v>
+        <v>0.000313475081687372</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003443756579971883</v>
+        <v>0.0003443756579971753</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0005292032383015064</v>
+        <v>0.0005292032383015009</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000486492039823441</v>
+        <v>0.0004864920398234371</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004062660015519795</v>
+        <v>0.0004062660015519755</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003348234117389403</v>
+        <v>0.0003348234117389352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003126922992806238</v>
+        <v>0.0003126922992806178</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0002281330541981362</v>
+        <v>0.0002281330541981357</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004212576174353773</v>
+        <v>0.0004212576174353729</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004007966428536892</v>
+        <v>0.0004007966428536835</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003382844549017621</v>
+        <v>0.0003382844549017567</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002245595724287695</v>
+        <v>0.0002245595724287653</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004693763191927111</v>
+        <v>0.0004693763191927046</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004209594284925937</v>
+        <v>0.0004209594284925882</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003067490176065086</v>
+        <v>0.000306749017606509</v>
       </c>
       <c r="U2" t="n">
-        <v>0.000199372939429247</v>
+        <v>0.0001993729394292411</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000384239015381535</v>
+        <v>0.000384239015381529</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001236273347592299</v>
+        <v>0.001236273347592293</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001266746932885919</v>
+        <v>0.001266746932885914</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0005280398158988607</v>
+        <v>0.0005280398158988548</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0004856081519755223</v>
+        <v>0.0004856081519755158</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008391478160184657</v>
+        <v>0.0008391478160184601</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.000134844698729012</v>
+        <v>0.0001348446987290118</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001315613060552637</v>
+        <v>0.0001315613060552654</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001827816250527548</v>
+        <v>0.0001827816250527464</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001521706796403687</v>
+        <v>0.0001521706796403682</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001377978996401237</v>
+        <v>0.0001377978996401233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001931395442467964</v>
+        <v>0.0001931395442467973</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001810305315515566</v>
+        <v>0.0001810305315515517</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001801322152834153</v>
+        <v>0.0001801322152834146</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001430283429971365</v>
+        <v>0.0001430283429971353</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001538930400307209</v>
+        <v>0.000153893040030712</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00015122984026497</v>
+        <v>0.0001512298402649694</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001215381446402893</v>
+        <v>0.0001215381446402915</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001576438981984762</v>
+        <v>0.0001576438981984745</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001650719507179696</v>
+        <v>0.0001650719507179634</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000182573860543114</v>
+        <v>0.0001825738605431067</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001262126279046021</v>
+        <v>0.0001262126279045961</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002332295283192201</v>
+        <v>0.0002332295283192132</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001306139078640316</v>
+        <v>0.0001306139078640284</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0001825638371753481</v>
+        <v>0.0001825638371753368</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000233809891086546</v>
+        <v>0.000233809891086545</v>
       </c>
     </row>
     <row r="4">
@@ -4866,82 +4866,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001433180925577606</v>
+        <v>0.001433180925577601</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001447527441368914</v>
+        <v>0.001447527441368903</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00146211335569533</v>
+        <v>0.001462113355695325</v>
       </c>
       <c r="E4" t="n">
         <v>0.001460416608280284</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001472204300840516</v>
+        <v>0.001472204300840515</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001484553290591502</v>
+        <v>0.001484553290591499</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001551920773257405</v>
+        <v>0.001551920773257399</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001536353042952366</v>
+        <v>0.00153635304295236</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001497222531534134</v>
+        <v>0.001497222531534135</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001481071608998514</v>
+        <v>0.001481071608998509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001473005078384101</v>
+        <v>0.001473005078384096</v>
       </c>
       <c r="M4" t="n">
         <v>0.001440638902230455</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001512575862013183</v>
+        <v>0.001512575862013176</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001505118077043047</v>
+        <v>0.001505118077043042</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001482333118589741</v>
+        <v>0.001482333118589738</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001440881734353328</v>
+        <v>0.001440881734353335</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001530114563765402</v>
+        <v>0.001530114563765397</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001512467175645046</v>
+        <v>0.00151246717564504</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001470838822003421</v>
+        <v>0.001470838822003419</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001431701502381379</v>
+        <v>0.001431701502381372</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001437368036549053</v>
+        <v>0.001437368036549049</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001809639525257485</v>
+        <v>0.00180963952525748</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001820746789258105</v>
+        <v>0.0018207467892581</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001551496719453237</v>
+        <v>0.001551496719453233</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001536030876210935</v>
+        <v>0.00153603087621093</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001664891932282252</v>
+        <v>0.001664891932282248</v>
       </c>
       <c r="AB4" t="n">
         <v>0.001406891402236528</v>
@@ -4954,37 +4954,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001406984958300964</v>
+        <v>0.001406984958300946</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001425792569869684</v>
+        <v>0.001425792569869668</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001412440435035842</v>
+        <v>0.001412440435035843</v>
       </c>
       <c r="F5" t="n">
         <v>0.001408172030889917</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001429429503033597</v>
+        <v>0.001429429503033593</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001415126847567402</v>
+        <v>0.0014151268475674</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="M5" t="n">
         <v>0.001423143160100349</v>
@@ -4993,46 +4993,46 @@
         <v>0.001411164558613529</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001415124613102556</v>
+        <v>0.001415124613102559</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001414153908060811</v>
+        <v>0.001414153908060812</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001403331633663111</v>
+        <v>0.001403331633663107</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="U5" t="n">
         <v>0.001416491756859903</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001357484215068788</v>
+        <v>0.001357484215068784</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001425578435392128</v>
+        <v>0.001425578435392125</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0014050354279224</v>
+        <v>0.001405035427922391</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001444041831467634</v>
+        <v>0.001444041831467627</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001406639642785173</v>
+        <v>0.001406639642785172</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001425574781992275</v>
+        <v>0.001425574781992267</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001442963052742887</v>
+        <v>0.001442963052742886</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001172681612262173</v>
+        <v>0.0001172681612262131</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000131614677017528</v>
+        <v>0.0001316146770175231</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000146200591343943</v>
+        <v>0.0001462005913439381</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001445038439288964</v>
+        <v>0.0001445038439288961</v>
       </c>
       <c r="F6" t="n">
         <v>0.0001562915364891284</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001581172093917236</v>
+        <v>0.0001581172093917157</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002360080089060184</v>
+        <v>0.0002360080089060132</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002204402786009773</v>
+        <v>0.0002204402786009735</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001801206365620842</v>
+        <v>0.0001801206365620799</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001651588446471262</v>
+        <v>0.0001651588446471214</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001570923140327126</v>
+        <v>0.0001570923140327085</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001247261378790696</v>
+        <v>0.0001247261378790693</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001966630976617892</v>
+        <v>0.0001966630976617869</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001786819958432632</v>
+        <v>0.0001786819958432593</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000155897037389958</v>
+        <v>0.0001558970373899532</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001249689700019405</v>
+        <v>0.0001249689700019469</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002142017994140151</v>
+        <v>0.0002142017994140109</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001965544112936565</v>
+        <v>0.0001965544112936526</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001549260576520347</v>
+        <v>0.0001549260576520331</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001052654211815957</v>
+        <v>0.0001052654211815918</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001710525925433348</v>
+        <v>0.0001710525925433359</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000483203444057701</v>
+        <v>0.0004832034440576959</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0004943107080583214</v>
+        <v>0.0004943107080583162</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002355839551018495</v>
+        <v>0.0002355839551018455</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002201181118595463</v>
+        <v>0.0002201181118595411</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0003489791679308654</v>
+        <v>0.0003489791679308608</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.097863788513966e-05</v>
+        <v>9.097863788513943e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.107219394957612e-05</v>
+        <v>9.107219394955918e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001098798055182981</v>
+        <v>0.0001098798055182862</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="E7" t="n">
-        <v>9.65276706844563e-05</v>
+        <v>9.652767068445598e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>9.22592665385296e-05</v>
+        <v>9.225926653852934e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001029934218338157</v>
+        <v>0.0001029934218338106</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="J7" t="n">
-        <v>9.802495259535135e-05</v>
+        <v>9.802495259534475e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001072303957489621</v>
+        <v>0.0001072303957489618</v>
       </c>
       <c r="N7" t="n">
-        <v>9.525179426214401e-05</v>
+        <v>9.525179426214093e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>8.868853190277541e-05</v>
+        <v>8.868853190277533e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>8.771782686102904e-05</v>
+        <v>8.771782686102874e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.741886931171878e-05</v>
+        <v>8.741886931171953e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="T7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="U7" t="n">
-        <v>9.005567566012054e-05</v>
+        <v>9.005567566012025e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>9.116877106307555e-05</v>
+        <v>9.116877106307258e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>9.914235419234508e-05</v>
+        <v>9.914235419234137e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>7.85993467226128e-05</v>
+        <v>7.859934672260685e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001281290671162462</v>
+        <v>0.0001281290671162405</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.072687843378625e-05</v>
+        <v>9.072687843378179e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.000109662017640887</v>
+        <v>0.0001096620176408828</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001270502883914998</v>
+        <v>0.0001270502883914994</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002651805313456831</v>
+        <v>0.0002651805313456812</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002367871361784395</v>
+        <v>0.0002367871361784396</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003051818706324059</v>
+        <v>0.0003051818706324015</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003463467005611251</v>
+        <v>0.0003463467005611253</v>
       </c>
       <c r="F2" t="n">
         <v>0.0002787434615789811</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002659076093077192</v>
+        <v>0.0002659076093077154</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003913372080467327</v>
+        <v>0.0003913372080467362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003152068189510437</v>
+        <v>0.0003152068189510416</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003620757839916999</v>
+        <v>0.0003620757839917044</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002499242253939821</v>
+        <v>0.0002499242253939796</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003190593561041929</v>
+        <v>0.0003190593561041912</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0002382286210730083</v>
+        <v>0.0002382286210730125</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0003254607277045292</v>
+        <v>0.0003254607277045269</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0005932939596902032</v>
+        <v>0.0005932939596902002</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003760945876660936</v>
+        <v>0.0003760945876660943</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002173358350190305</v>
+        <v>0.0002173358350190278</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004655375334590103</v>
+        <v>0.0004655375334590085</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003626225752748259</v>
+        <v>0.0003626225752748187</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0002516600859101582</v>
+        <v>0.0002516600859101552</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002303154105346668</v>
+        <v>0.000230315410534663</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0004358745802405611</v>
+        <v>0.0004358745802405614</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001009670094111271</v>
+        <v>0.001009670094111269</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001534778818935551</v>
+        <v>0.00153477881893555</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0004776627185690388</v>
+        <v>0.0004776627185690373</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0003809297887095695</v>
+        <v>0.0003809297887095645</v>
       </c>
       <c r="AA2" t="n">
         <v>0.000884629931482735</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0002142938531436995</v>
+        <v>0.0002142938531436926</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001293435665191297</v>
+        <v>0.0001293435665191304</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001801438848515535</v>
+        <v>0.0001801438848515534</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001501224781414984</v>
+        <v>0.0001501224781414983</v>
       </c>
       <c r="F3" t="n">
         <v>0.0001356577671772693</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001901237469952949</v>
+        <v>0.0001901237469952927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001783614387347507</v>
+        <v>0.0001783614387347529</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001775899344494642</v>
+        <v>0.0001775899344494681</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001406619899640658</v>
+        <v>0.0001406619899640609</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001513858798624456</v>
+        <v>0.0001513858798624335</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001487571953278749</v>
+        <v>0.0001487571953278722</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000119450305886423</v>
+        <v>0.0001194503058864181</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001550922781487214</v>
+        <v>0.0001550922781487218</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001628535694091543</v>
+        <v>0.0001628535694091542</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0001796949951949574</v>
+        <v>0.0001796949951949464</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001240642075626692</v>
+        <v>0.0001240642075626696</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002297012643886433</v>
+        <v>0.0002297012643886359</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001284084466662011</v>
+        <v>0.0001284084466662008</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000179685101731301</v>
+        <v>0.0001796851017312967</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002308409440528438</v>
+        <v>0.0002308409440528472</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001450053781033704</v>
+        <v>0.001450053781033701</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001439996283967547</v>
+        <v>0.001439996283967548</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001464633799484274</v>
+        <v>0.001464633799484269</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001477885637521063</v>
+        <v>0.001477885637521064</v>
       </c>
       <c r="F4" t="n">
         <v>0.00145402597960672</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001450318792413085</v>
+        <v>0.001450318792413081</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001496036408284748</v>
+        <v>0.001496036408284746</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00146828777542753</v>
+        <v>0.001468287775427527</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001476387469880262</v>
+        <v>0.001476387469880259</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001444493036662899</v>
+        <v>0.00144449303666289</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001469691979981079</v>
+        <v>0.001469691979981076</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001438898622814326</v>
+        <v>0.001438898622814329</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001472025204760701</v>
+        <v>0.001472025204760697</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001569647272762881</v>
+        <v>0.001569647272762878</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001490480652143891</v>
+        <v>0.001490480652143886</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001432614951043429</v>
+        <v>0.001432614951043425</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001523081555593309</v>
+        <v>0.001523081555593306</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001485570261823627</v>
+        <v>0.001485570261823621</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001445125737437543</v>
+        <v>0.00144512573743754</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001437345853905007</v>
+        <v>0.001437345853905001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001456009332066971</v>
+        <v>0.001456009332066975</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001721411484423938</v>
+        <v>0.001721411484423935</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00191280744848443</v>
+        <v>0.001912807448484421</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001527501043184803</v>
+        <v>0.001527501043184799</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00149224302614644</v>
+        <v>0.001492243026146436</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00167583581344156</v>
+        <v>0.001675835813441552</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001430597338638753</v>
+        <v>0.001430597338638741</v>
       </c>
     </row>
     <row r="5">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0014005428024326</v>
+        <v>0.001400542802432597</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001419350483997536</v>
+        <v>0.001419350483997537</v>
       </c>
       <c r="D5" t="n">
         <v>0.00141889170087728</v>
@@ -5650,10 +5650,10 @@
         <v>0.001406364212630263</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001401872924194348</v>
+        <v>0.001401872924194347</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001422696464499244</v>
+        <v>0.001422696464499247</v>
       </c>
       <c r="H5" t="n">
         <v>0.00141889170087728</v>
@@ -5662,7 +5662,7 @@
         <v>0.00141889170087728</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001409425748316866</v>
+        <v>0.001409425748316862</v>
       </c>
       <c r="K5" t="n">
         <v>0.00141889170087728</v>
@@ -5671,19 +5671,19 @@
         <v>0.00141889170087728</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001416796533595453</v>
+        <v>0.001416796533595457</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001404668234870634</v>
+        <v>0.001404668234870632</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001408576966812319</v>
+        <v>0.00140857696681232</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001407618842167052</v>
+        <v>0.001407618842167044</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001396936825104507</v>
+        <v>0.001396936825104503</v>
       </c>
       <c r="R5" t="n">
         <v>0.00141889170087728</v>
@@ -5695,28 +5695,28 @@
         <v>0.00141889170087728</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001409927905464947</v>
+        <v>0.001409927905464944</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001356496379593497</v>
+        <v>0.001356496379593501</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001418895306928607</v>
+        <v>0.001418895306928605</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001398618538086335</v>
+        <v>0.001398618538086327</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001437122004846452</v>
+        <v>0.001437122004846447</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001400201962226938</v>
+        <v>0.001400201962226936</v>
       </c>
       <c r="AA5" t="n">
         <v>0.00141889170087728</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001436628558969385</v>
+        <v>0.001436628558969375</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001389812669946233</v>
+        <v>0.0001389812669946129</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001289237699284595</v>
+        <v>0.0001289237699284594</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001535612854451915</v>
+        <v>0.0001535612854451814</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001668131234819763</v>
+        <v>0.0001668131234819762</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001429534655676319</v>
+        <v>0.000142953465567632</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001287682517301585</v>
+        <v>0.0001287682517301568</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001849638942456651</v>
+        <v>0.0001849638942456567</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001572152613884499</v>
+        <v>0.0001572152613884393</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001633943070224352</v>
+        <v>0.0001633943070224327</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001334205226238172</v>
+        <v>0.0001334205226238034</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001586194659419977</v>
+        <v>0.0001586194659419872</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001278261087752378</v>
+        <v>0.0001278261087752413</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001609526907216193</v>
+        <v>0.000160952690721609</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002480967320799549</v>
+        <v>0.0002480967320799519</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001689301114609644</v>
+        <v>0.0001689301114609598</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001215424370043465</v>
+        <v>0.0001215424370043373</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002120090415542286</v>
+        <v>0.0002120090415542188</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001744977477845453</v>
+        <v>0.0001744977477845322</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000134053223398459</v>
+        <v>0.0001340532233984499</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001157953132220802</v>
+        <v>0.0001157953132220745</v>
       </c>
       <c r="V6" t="n">
         <v>0.0001894171248699482</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003998609437410125</v>
+        <v>0.0003998609437410091</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0005912569078015055</v>
+        <v>0.0005912569078014972</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002164285291457223</v>
+        <v>0.0002164285291457107</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001811705121073525</v>
+        <v>0.0001811705121073456</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0003647632994024767</v>
+        <v>0.0003647632994024637</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001195248245996654</v>
+        <v>0.000119524824599658</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.947028839351116e-05</v>
+        <v>8.94702883935104e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001082779699584481</v>
+        <v>0.000108277969958448</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="E7" t="n">
-        <v>9.529169859117504e-05</v>
+        <v>9.529169859117497e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>9.080041015526127e-05</v>
+        <v>9.080041015526123e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001011459238163189</v>
+        <v>0.0001011459238163218</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="J7" t="n">
-        <v>9.643258545903454e-05</v>
+        <v>9.643258545903329e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000105724019556364</v>
+        <v>0.0001057240195563679</v>
       </c>
       <c r="N7" t="n">
-        <v>9.359572083155376e-05</v>
+        <v>9.359572083154405e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>8.702642612939333e-05</v>
+        <v>8.702642612939417e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>8.606830148412638e-05</v>
+        <v>8.60683014841191e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.586431106541938e-05</v>
+        <v>8.586431106541708e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="U7" t="n">
-        <v>8.837736478202098e-05</v>
+        <v>8.837736478201727e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>8.990417239647268e-05</v>
+        <v>8.990417239647256e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>9.734476624567926e-05</v>
+        <v>9.734476624567872e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>7.706799740340833e-05</v>
+        <v>7.70679974034e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001260494908073675</v>
+        <v>0.000126049490807357</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.912944818784608e-05</v>
+        <v>8.91294481878476e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001078191868381927</v>
+        <v>0.0001078191868381916</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000125556044930297</v>
+        <v>0.0001255560449302884</v>
       </c>
     </row>
   </sheetData>
@@ -6058,82 +6058,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007754900625408284</v>
+        <v>0.0007754900625408535</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002536251243872272</v>
+        <v>0.0002536251243872423</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009484436616082621</v>
+        <v>0.0009484436616082884</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000427646311024083</v>
+        <v>0.0004276463110240993</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005128601698335712</v>
+        <v>0.0005128601698335714</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001163669478444898</v>
+        <v>0.001163669478444926</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001478582876106353</v>
+        <v>0.001478582876106379</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001173387107683549</v>
+        <v>0.001173387107683571</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001244677281233195</v>
+        <v>0.001244677281233204</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001610238868676791</v>
+        <v>0.001610238868676814</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001198915793220153</v>
+        <v>0.001198915793220178</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003718987105269639</v>
+        <v>0.00371898710526964</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00147927501612631</v>
+        <v>0.001479275016126332</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0007835928925279023</v>
+        <v>0.0007835928925279248</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0009932989514121052</v>
+        <v>0.0009932989514121191</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0006840760177205143</v>
+        <v>0.0006840760177205374</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00119658506332237</v>
+        <v>0.001196585063322357</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0009291756964943357</v>
+        <v>0.00092917569649436</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001151621724782743</v>
+        <v>0.001151621724782768</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001468703583406896</v>
+        <v>0.001468703583406927</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0005323331613934099</v>
+        <v>0.0005323331613934117</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001741458320724986</v>
+        <v>0.001741458320725014</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001486530236363514</v>
+        <v>0.001486530236363542</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001160571642634188</v>
+        <v>0.001160571642634211</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0007776246986829615</v>
+        <v>0.0007776246986829834</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001575321080953769</v>
+        <v>0.001575321080953791</v>
       </c>
       <c r="AB2" t="n">
         <v>0.001954261140789346</v>
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000152848077679774</v>
+        <v>0.00015284807767981</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002092623338970009</v>
+        <v>0.000209262333897</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001747625778943245</v>
+        <v>0.0001747625778943391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001588916772505052</v>
+        <v>0.000158891677250505</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002225092558532817</v>
+        <v>0.0002225092558532884</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000208598956213312</v>
+        <v>0.0002085989562133173</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002159924262434475</v>
+        <v>0.0002159924262434472</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001658203114937167</v>
+        <v>0.0001658203114937373</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001781111405001206</v>
+        <v>0.0001781111405001324</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001750983613277663</v>
+        <v>0.0001750983613277963</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001415092467247713</v>
+        <v>0.0001415092467247758</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001823543294716152</v>
+        <v>0.0001823543294716171</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001892720705995363</v>
+        <v>0.0001892720705995435</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002105566895562801</v>
+        <v>0.0002105566895563165</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001467973163656609</v>
+        <v>0.0001467973163656952</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002678615382083522</v>
+        <v>0.0002678615382083659</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001517763212248696</v>
+        <v>0.0001517763212248753</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002105453504819914</v>
+        <v>0.0002105453504820144</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002732145844692133</v>
+        <v>0.0002732145844692139</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001701684715857602</v>
+        <v>0.001701684715857647</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00151065570184241</v>
+        <v>0.001510655701842435</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001764724271793981</v>
+        <v>0.001764724271794035</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001571683633483416</v>
+        <v>0.001571683633483439</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001604087646497885</v>
+        <v>0.001604087646497895</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001843171554721803</v>
+        <v>0.001843171554721838</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001957953790269583</v>
+        <v>0.001957953790269624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001846713516469123</v>
+        <v>0.001846713516469175</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001855813061505191</v>
+        <v>0.001855813061505197</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002005940853578793</v>
+        <v>0.002005940853578833</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001856018422574252</v>
+        <v>0.001856018422574293</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002778016504254099</v>
+        <v>0.002778016504254121</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001958206067179343</v>
+        <v>0.001958206067179381</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001704638102239657</v>
+        <v>0.001704638102239696</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001781073498210083</v>
+        <v>0.001781073498210117</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001668365369958511</v>
+        <v>0.001668365369958549</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001855168898895326</v>
+        <v>0.001855168898895365</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001757701324765829</v>
+        <v>0.001757701324765865</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001838780289983809</v>
+        <v>0.001838780289983851</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00195435290408914</v>
+        <v>0.001954352904089183</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001505181176869393</v>
+        <v>0.001505181176869391</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002053768802993758</v>
+        <v>0.002053768802993814</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001960850509760707</v>
+        <v>0.001960850509760749</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00184204242994542</v>
+        <v>0.001842042429945469</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001702462765665245</v>
+        <v>0.001702462765665292</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001993213729979116</v>
+        <v>0.001993213729979164</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002132857911154337</v>
+        <v>0.002132857911154352</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001474739023807069</v>
+        <v>0.00147473902380713</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001494485985642912</v>
+        <v>0.001494485985642927</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001479510482268336</v>
+        <v>0.001479510482268374</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001475070287459246</v>
+        <v>0.001475070287459255</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001500129705248465</v>
+        <v>0.001500129705248505</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001478174678281383</v>
+        <v>0.001478174678281423</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001501216077989348</v>
+        <v>0.00150121607798936</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001479467250704597</v>
+        <v>0.001479467250704628</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00148394711355123</v>
+        <v>0.001483947113551237</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001482848990920746</v>
+        <v>0.001482848990920773</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001470606153071251</v>
+        <v>0.001470606153071294</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001485493706105299</v>
+        <v>0.001485493706105347</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001380139437701742</v>
+        <v>0.00138013943770175</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001495773135187325</v>
+        <v>0.001495773135187365</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00147253359235971</v>
+        <v>0.001472533592359765</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001516660079613504</v>
+        <v>0.001516660079613512</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001474348381164464</v>
+        <v>0.001474348381164515</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0014957690022279</v>
+        <v>0.001495769002227934</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001520136181220932</v>
+        <v>0.001520136181220952</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0003328225370449923</v>
+        <v>0.0003328225370450218</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001417935230298038</v>
+        <v>0.0001417935230298046</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0003958620929813746</v>
+        <v>0.0003958620929814066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002028214546708048</v>
+        <v>0.0002028214546708182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002352254676852714</v>
+        <v>0.0002352254676852711</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000463572138737103</v>
+        <v>0.0004635721387371288</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005890916114569759</v>
+        <v>0.0005890916114570026</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000477851337656516</v>
+        <v>0.0004778513376565427</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004922931463715843</v>
+        <v>0.0004922931463716039</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0006370786747661825</v>
+        <v>0.0006370786747662057</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004871562437616494</v>
+        <v>0.0004871562437616724</v>
       </c>
       <c r="M6" t="n">
         <v>0.001409154325441489</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000589343888366733</v>
+        <v>0.0005893438883667582</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003250386862549592</v>
+        <v>0.0003250386862549879</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0004014740822253814</v>
+        <v>0.0004014740822253958</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002995031911458996</v>
+        <v>0.0002995031911459269</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004863067200827174</v>
+        <v>0.0004863067200827484</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003888391459532205</v>
+        <v>0.0003888391459532461</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0004699181111712019</v>
+        <v>0.0004699181111712284</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005747534881044439</v>
+        <v>0.0005747534881044653</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002306471171639807</v>
+        <v>0.0002306471171639773</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000674169387009059</v>
+        <v>0.0006741693870090983</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0005812510937760056</v>
+        <v>0.0005812510937760363</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0004731802511328122</v>
+        <v>0.0004731802511328381</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0003336005868526379</v>
+        <v>0.0003336005868526643</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006243515511665073</v>
+        <v>0.0006243515511665336</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0007639957323417245</v>
+        <v>0.0007639957323417249</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001058768449944625</v>
+        <v>0.0001058768449944979</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001256238068302988</v>
+        <v>0.000125623806830298</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001106483034557263</v>
+        <v>0.0001106483034557389</v>
       </c>
       <c r="F7" t="n">
         <v>0.0001062081086466372</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001205302892637634</v>
+        <v>0.0001205302892637927</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001146547631477769</v>
+        <v>0.0001146547631477905</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001323538991767388</v>
+        <v>0.0001323538991767389</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001106050718919886</v>
+        <v>0.0001106050718920052</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001043476975665292</v>
+        <v>0.0001043476975665313</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001032495749360439</v>
+        <v>0.000103249574936058</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001017439742586419</v>
+        <v>0.0001017439742586662</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001058942901205991</v>
+        <v>0.0001058942901206269</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001056053779963318</v>
+        <v>0.0001056053779963277</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001161737192026283</v>
+        <v>0.0001161737192026587</v>
       </c>
       <c r="X7" t="n">
-        <v>9.293417637500729e-05</v>
+        <v>9.293417637504371e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.000147797900800891</v>
+        <v>0.0001477979008008916</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001054862023518507</v>
+        <v>0.0001054862023518841</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001269068234152897</v>
+        <v>0.0001269068234153138</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001512740024083232</v>
+        <v>0.0001512740024083233</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001689922193377896</v>
+        <v>0.000168992219337791</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002387173769763819</v>
+        <v>0.000238717376976382</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003410917686799257</v>
+        <v>0.000341091768679927</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002830603581187853</v>
+        <v>0.0002830603581187857</v>
       </c>
       <c r="F2" t="n">
         <v>0.0002549817363424608</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001046809049778141</v>
+        <v>0.001046809049778143</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0009946274578744739</v>
+        <v>0.0009946274578744752</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004204918794333705</v>
+        <v>0.0004204918794333723</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007182181361650326</v>
+        <v>0.0007182181361650299</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006898576563529607</v>
+        <v>0.0006898576563529625</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006812550390819827</v>
+        <v>0.000681255039081984</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000505490802558377</v>
+        <v>0.0005054908025583771</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004938199785887232</v>
+        <v>0.0004938199785887246</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0003156493923316193</v>
+        <v>0.0003156493923316207</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007343053572812938</v>
+        <v>0.0007343053572812947</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000401785809385649</v>
+        <v>0.0004017858093856507</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0006277959436844938</v>
+        <v>0.0006277959436844952</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004750948148996503</v>
+        <v>0.0004750948148996519</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004531555685793753</v>
+        <v>0.0004531555685793757</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003770305893379294</v>
+        <v>0.0003770305893379315</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0004178553933382139</v>
+        <v>0.0004178553933382137</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001502573046209157</v>
+        <v>0.001502573046209158</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001519281489196574</v>
+        <v>0.001519281489196576</v>
       </c>
       <c r="Y2" t="n">
         <v>0.001700362941508386</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0004235474534049481</v>
+        <v>0.0004235474534049493</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008103024621889045</v>
+        <v>0.0008103024621889048</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004289901590799161</v>
+        <v>0.004289901590799162</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001415928565223981</v>
+        <v>0.0001415928565223995</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000195430856691441</v>
+        <v>0.0001954308566914409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001630037652057539</v>
+        <v>0.000163003765205754</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001475890709361872</v>
+        <v>0.0001475890709361873</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002066683703195172</v>
+        <v>0.0002066683703195188</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001937932700654399</v>
+        <v>0.0001937932700654408</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001934189194175239</v>
+        <v>0.000193418919417524</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001537111525746528</v>
+        <v>0.0001537111525746539</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001651928994155019</v>
+        <v>0.0001651928994155028</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001623784458320406</v>
+        <v>0.0001623784458320428</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0001310004394904187</v>
+        <v>0.0001310004394904203</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001691530564709106</v>
+        <v>0.0001691530564709115</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001766393962102378</v>
+        <v>0.0001766393962102379</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0001955026189827717</v>
+        <v>0.0001955026189827734</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001359404054467165</v>
+        <v>0.0001359404054467175</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000249028849162004</v>
+        <v>0.0002490288491620055</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001405916517802698</v>
+        <v>0.0001405916517802712</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0001954920263436072</v>
+        <v>0.0001954920263436088</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000263806127370916</v>
+        <v>0.0002638061273709164</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001456728871386949</v>
+        <v>0.001456728871386951</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001482103998559837</v>
+        <v>0.001482103998559836</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001519457136227218</v>
+        <v>0.001519457136227219</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0014958977048555</v>
+        <v>0.001495897704855499</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001486545401680779</v>
+        <v>0.001486545401680778</v>
       </c>
       <c r="G4" t="n">
         <v>0.001776682798236813</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001757663220735112</v>
+        <v>0.001757663220735115</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001548397544233674</v>
+        <v>0.001548397544233677</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00164304478746584</v>
+        <v>0.001643044787465841</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001646578206868218</v>
+        <v>0.00164657820686822</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001643442653889979</v>
+        <v>0.001643442653889982</v>
       </c>
       <c r="M4" t="n">
         <v>0.001578061169809818</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001575124775313788</v>
+        <v>0.00157512477531379</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001510183688807728</v>
+        <v>0.00151018368880773</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001662778871925339</v>
+        <v>0.001662778871925342</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001541579401359044</v>
+        <v>0.001541579401359046</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001623957441365985</v>
+        <v>0.001623957441365987</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001568299673031094</v>
+        <v>0.001568299673031097</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001560303075370991</v>
+        <v>0.001560303075370994</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001532556414342122</v>
+        <v>0.001532556414342125</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001459502107658629</v>
+        <v>0.001459502107658626</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001942803423084865</v>
+        <v>0.001942803423084868</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001948893454353339</v>
+        <v>0.001948893454353341</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002014895517355226</v>
+        <v>0.002014895517355227</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001549511265065955</v>
+        <v>0.001549511265065956</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001690478924261101</v>
+        <v>0.001690478924261103</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00296638565778147</v>
+        <v>0.002966385657781471</v>
       </c>
     </row>
     <row r="5">
@@ -7012,10 +7012,10 @@
         <v>0.001466326570211956</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001452138486514388</v>
+        <v>0.001452138486514389</v>
       </c>
       <c r="F5" t="n">
         <v>0.001447402036208537</v>
@@ -7024,67 +7024,67 @@
         <v>0.001470461386004088</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001451898081880228</v>
+        <v>0.00145189808188023</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="M5" t="n">
         <v>0.001464314632938042</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001451159101991131</v>
+        <v>0.001451159101991132</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001455344063889143</v>
+        <v>0.001455344063889144</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001454318228606953</v>
+        <v>0.001454318228606955</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001442881313754586</v>
+        <v>0.001442881313754588</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001456787494633327</v>
+        <v>0.001456787494633328</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001371581709206728</v>
+        <v>0.001371581709206723</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001466391600756715</v>
+        <v>0.001466391600756717</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001444681873337647</v>
+        <v>0.001444681873337648</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001485901283120319</v>
+        <v>0.00148590128312032</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001446377198008537</v>
+        <v>0.001446377198008538</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001466387739864125</v>
+        <v>0.001466387739864127</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001498921138161715</v>
+        <v>0.001498921138161716</v>
       </c>
     </row>
     <row r="6">
@@ -7094,82 +7094,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001082835003194145</v>
+        <v>0.0001082835003194159</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001336586274923022</v>
+        <v>0.000133658627492302</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001710117651596845</v>
+        <v>0.0001710117651596856</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001474523337879645</v>
+        <v>0.0001474523337879646</v>
       </c>
       <c r="F6" t="n">
         <v>0.0001381000306132449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004176238995849391</v>
+        <v>0.0004176238995849406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004092178496675809</v>
+        <v>0.0004092178496675817</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001999521731661416</v>
+        <v>0.0001999521731661427</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002971994606102919</v>
+        <v>0.0002971994606102929</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002981328358006841</v>
+        <v>0.0002981328358006853</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002949972828224448</v>
+        <v>0.0002949972828224461</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002296157987422821</v>
+        <v>0.0002296157987422822</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002266794042462544</v>
+        <v>0.0002266794042462563</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000151124790155854</v>
+        <v>0.0001511247901558557</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0003037199732734663</v>
+        <v>0.0003037199732734678</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001931340302915116</v>
+        <v>0.0001931340302915127</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002755120702984518</v>
+        <v>0.0002755120702984529</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002198543019635607</v>
+        <v>0.0002198543019635619</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0002118577043034566</v>
+        <v>0.0002118577043034588</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001734975156902484</v>
+        <v>0.0001734975156902506</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001864296697711193</v>
+        <v>0.0001864296697711194</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0005837445244329944</v>
+        <v>0.0005837445244329966</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0005898345557014666</v>
+        <v>0.000589834555701468</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0006664501462876925</v>
+        <v>0.0006664501462876939</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002010658939984205</v>
+        <v>0.0002010658939984215</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0003420335531935686</v>
+        <v>0.0003420335531935697</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001617940286713942</v>
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.829675431276756e-05</v>
+        <v>9.829675431276783e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000117881199144425</v>
+        <v>0.0001178811991444251</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001036931154468551</v>
       </c>
       <c r="F7" t="n">
-        <v>9.895666514100405e-05</v>
+        <v>9.895666514100399e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001114024873522138</v>
+        <v>0.000111402487352215</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000106052755024679</v>
+        <v>0.0001060527550246798</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="M7" t="n">
         <v>0.0001158692618705073</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001027137309235983</v>
+        <v>0.0001027137309235979</v>
       </c>
       <c r="O7" t="n">
-        <v>9.628516523726882e-05</v>
+        <v>9.628516523726978e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>9.525932995508014e-05</v>
+        <v>9.5259329955081e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.443594268705155e-05</v>
+        <v>9.443594268705205e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="U7" t="n">
-        <v>9.772859598145362e-05</v>
+        <v>9.772859598145432e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>9.850927131921731e-05</v>
+        <v>9.85092713192175e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001073327021048423</v>
+        <v>0.0001073327021048434</v>
       </c>
       <c r="X7" t="n">
-        <v>8.562297468577266e-05</v>
+        <v>8.562297468577442e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001374559120527846</v>
+        <v>0.0001374559120527844</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.793182694100106e-05</v>
+        <v>9.793182694100173e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001179423687965921</v>
+        <v>0.000117942368796592</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001504757670941821</v>
+        <v>0.0001504757670941822</v>
       </c>
     </row>
   </sheetData>
